--- a/Documentation/SRS_HVPSU_Test_Results.xlsx
+++ b/Documentation/SRS_HVPSU_Test_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\home\jek48386\repos\SRS300\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2985331-0F0B-472F-AA27-ABBDDF0D4B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{442D95D0-0ED6-48A2-B7EC-ED21C98754DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-1875" windowWidth="29040" windowHeight="15720" xr2:uid="{ABB50434-DF5E-4618-8107-94BD17379F73}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="223">
   <si>
     <t>Test</t>
   </si>
@@ -881,6 +881,14 @@
   </si>
   <si>
     <t>Deploy a second instance of the IOC</t>
+  </si>
+  <si>
+    <t>Errors when trying to deploy, did 
+not deploy.</t>
+  </si>
+  <si>
+    <t>Prefix contained a colon which
+ caused an error so it was removed and put into the PV name instead, Prefix was in two parts "$(P)$(R)" which caused some issues so it was changed to "$(DEVICE)"</t>
   </si>
 </sst>
 </file>
@@ -1665,7 +1673,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="227">
+  <cellXfs count="231">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1980,288 +1988,300 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2271,8 +2291,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFFFCC"/>
       <color rgb="FFEDFDCF"/>
-      <color rgb="FFFFFFCC"/>
       <color rgb="FFF9FEE2"/>
       <color rgb="FFF6FECE"/>
       <color rgb="FFDDFFFF"/>
@@ -2609,7 +2629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A62839A-462D-4B14-AC2D-C7655127CCDA}">
-  <dimension ref="A1:M119"/>
+  <dimension ref="A1:M120"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19.28515625" style="1" customWidth="1"/>
@@ -2626,34 +2646,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="127" t="s">
+      <c r="A1" s="217" t="s">
         <v>211</v>
       </c>
-      <c r="B1" s="128"/>
+      <c r="B1" s="218"/>
       <c r="C1" s="122"/>
       <c r="D1" s="123"/>
       <c r="E1" s="121"/>
       <c r="F1" s="121"/>
     </row>
     <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="129" t="s">
+      <c r="A2" s="219" t="s">
         <v>210</v>
       </c>
-      <c r="B2" s="130"/>
-      <c r="C2" s="130"/>
-      <c r="D2" s="130"/>
-      <c r="E2" s="131"/>
+      <c r="B2" s="220"/>
+      <c r="C2" s="220"/>
+      <c r="D2" s="220"/>
+      <c r="E2" s="221"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="132" t="s">
+      <c r="A3" s="215" t="s">
         <v>212</v>
       </c>
-      <c r="B3" s="133"/>
-      <c r="C3" s="133"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="133"/>
+      <c r="B3" s="222"/>
+      <c r="C3" s="222"/>
+      <c r="D3" s="222"/>
+      <c r="E3" s="222"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
     </row>
@@ -2666,10 +2686,10 @@
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="1:13" s="4" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="163" t="s">
+      <c r="B6" s="202" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="164"/>
+      <c r="C6" s="203"/>
       <c r="D6" s="24" t="s">
         <v>206</v>
       </c>
@@ -2688,21 +2708,21 @@
       <c r="I6" s="86" t="s">
         <v>132</v>
       </c>
-      <c r="K6" s="155" t="s">
+      <c r="K6" s="201" t="s">
         <v>147</v>
       </c>
-      <c r="L6" s="155"/>
+      <c r="L6" s="201"/>
     </row>
     <row r="7" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="165" t="s">
+      <c r="B7" s="204" t="s">
         <v>59</v>
       </c>
-      <c r="C7" s="166"/>
-      <c r="D7" s="166"/>
-      <c r="E7" s="166"/>
-      <c r="F7" s="166"/>
-      <c r="G7" s="166"/>
-      <c r="H7" s="166"/>
+      <c r="C7" s="205"/>
+      <c r="D7" s="205"/>
+      <c r="E7" s="205"/>
+      <c r="F7" s="205"/>
+      <c r="G7" s="205"/>
+      <c r="H7" s="205"/>
       <c r="I7" s="91"/>
       <c r="K7" s="13"/>
       <c r="L7" s="3" t="s">
@@ -2728,24 +2748,24 @@
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="156" t="s">
+      <c r="B9" s="180" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="145" t="s">
+      <c r="C9" s="191" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="159"/>
-      <c r="E9" s="162" t="s">
+      <c r="D9" s="197"/>
+      <c r="E9" s="198" t="s">
         <v>69</v>
       </c>
-      <c r="F9" s="173" t="s">
-        <v>130</v>
-      </c>
-      <c r="G9" s="167">
+      <c r="F9" s="212" t="s">
+        <v>130</v>
+      </c>
+      <c r="G9" s="206">
         <v>45992</v>
       </c>
-      <c r="H9" s="170"/>
-      <c r="I9" s="148" t="s">
+      <c r="H9" s="209"/>
+      <c r="I9" s="166" t="s">
         <v>131</v>
       </c>
       <c r="K9" s="15"/>
@@ -2754,38 +2774,38 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="157"/>
-      <c r="C10" s="146"/>
-      <c r="D10" s="160"/>
-      <c r="E10" s="141"/>
-      <c r="F10" s="174"/>
-      <c r="G10" s="168"/>
-      <c r="H10" s="171"/>
-      <c r="I10" s="136"/>
+      <c r="B10" s="165"/>
+      <c r="C10" s="174"/>
+      <c r="D10" s="182"/>
+      <c r="E10" s="176"/>
+      <c r="F10" s="213"/>
+      <c r="G10" s="207"/>
+      <c r="H10" s="210"/>
+      <c r="I10" s="170"/>
       <c r="K10" s="19"/>
       <c r="L10" s="2" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="157"/>
-      <c r="C11" s="146"/>
-      <c r="D11" s="160"/>
-      <c r="E11" s="141"/>
-      <c r="F11" s="174"/>
-      <c r="G11" s="168"/>
-      <c r="H11" s="171"/>
-      <c r="I11" s="136"/>
+      <c r="B11" s="165"/>
+      <c r="C11" s="174"/>
+      <c r="D11" s="182"/>
+      <c r="E11" s="176"/>
+      <c r="F11" s="213"/>
+      <c r="G11" s="207"/>
+      <c r="H11" s="210"/>
+      <c r="I11" s="170"/>
     </row>
     <row r="12" spans="1:13" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="158"/>
-      <c r="C12" s="147"/>
-      <c r="D12" s="161"/>
-      <c r="E12" s="144"/>
-      <c r="F12" s="175"/>
-      <c r="G12" s="169"/>
-      <c r="H12" s="172"/>
-      <c r="I12" s="137"/>
+      <c r="B12" s="153"/>
+      <c r="C12" s="155"/>
+      <c r="D12" s="157"/>
+      <c r="E12" s="177"/>
+      <c r="F12" s="214"/>
+      <c r="G12" s="208"/>
+      <c r="H12" s="211"/>
+      <c r="I12" s="167"/>
       <c r="M12" s="12"/>
     </row>
     <row r="13" spans="1:13" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2833,13 +2853,13 @@
       </c>
     </row>
     <row r="15" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="176" t="s">
+      <c r="B15" s="152" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="134" t="s">
+      <c r="C15" s="185" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="134" t="s">
+      <c r="D15" s="185" t="s">
         <v>73</v>
       </c>
       <c r="E15" s="37" t="s">
@@ -2852,14 +2872,14 @@
         <v>45989</v>
       </c>
       <c r="H15" s="93"/>
-      <c r="I15" s="148" t="s">
+      <c r="I15" s="166" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="158"/>
-      <c r="C16" s="135"/>
-      <c r="D16" s="135"/>
+      <c r="B16" s="153"/>
+      <c r="C16" s="187"/>
+      <c r="D16" s="187"/>
       <c r="E16" s="31" t="s">
         <v>74</v>
       </c>
@@ -2870,7 +2890,7 @@
         <v>45989</v>
       </c>
       <c r="H16" s="94"/>
-      <c r="I16" s="137"/>
+      <c r="I16" s="167"/>
     </row>
     <row r="17" spans="2:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="63" t="s">
@@ -2911,13 +2931,13 @@
       <c r="I18" s="85"/>
     </row>
     <row r="19" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="156" t="s">
+      <c r="B19" s="180" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="132" t="s">
+      <c r="C19" s="215" t="s">
         <v>79</v>
       </c>
-      <c r="D19" s="145"/>
+      <c r="D19" s="191"/>
       <c r="E19" s="22" t="s">
         <v>77</v>
       </c>
@@ -2928,14 +2948,14 @@
         <v>45992</v>
       </c>
       <c r="H19" s="96"/>
-      <c r="I19" s="150" t="s">
+      <c r="I19" s="168" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="157"/>
-      <c r="C20" s="177"/>
-      <c r="D20" s="146"/>
+      <c r="B20" s="165"/>
+      <c r="C20" s="186"/>
+      <c r="D20" s="174"/>
       <c r="E20" s="5" t="s">
         <v>78</v>
       </c>
@@ -2946,12 +2966,12 @@
         <v>45992</v>
       </c>
       <c r="H20" s="74"/>
-      <c r="I20" s="136"/>
+      <c r="I20" s="170"/>
     </row>
     <row r="21" spans="2:9" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="158"/>
-      <c r="C21" s="135"/>
-      <c r="D21" s="147"/>
+      <c r="B21" s="153"/>
+      <c r="C21" s="187"/>
+      <c r="D21" s="155"/>
       <c r="E21" s="31" t="s">
         <v>80</v>
       </c>
@@ -2962,16 +2982,16 @@
         <v>45992</v>
       </c>
       <c r="H21" s="94"/>
-      <c r="I21" s="137"/>
+      <c r="I21" s="167"/>
     </row>
     <row r="22" spans="2:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="B22" s="176" t="s">
+      <c r="B22" s="152" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="134" t="s">
+      <c r="C22" s="185" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="134"/>
+      <c r="D22" s="185"/>
       <c r="E22" s="30" t="s">
         <v>81</v>
       </c>
@@ -2982,14 +3002,14 @@
         <v>45992</v>
       </c>
       <c r="H22" s="93"/>
-      <c r="I22" s="148" t="s">
+      <c r="I22" s="166" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="23" spans="2:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="158"/>
-      <c r="C23" s="135"/>
-      <c r="D23" s="135"/>
+      <c r="B23" s="153"/>
+      <c r="C23" s="187"/>
+      <c r="D23" s="187"/>
       <c r="E23" s="31" t="s">
         <v>82</v>
       </c>
@@ -3000,16 +3020,16 @@
         <v>45992</v>
       </c>
       <c r="H23" s="94"/>
-      <c r="I23" s="137"/>
+      <c r="I23" s="167"/>
     </row>
     <row r="24" spans="2:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="B24" s="176" t="s">
+      <c r="B24" s="152" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="134" t="s">
+      <c r="C24" s="185" t="s">
         <v>27</v>
       </c>
-      <c r="D24" s="134"/>
+      <c r="D24" s="185"/>
       <c r="E24" s="30" t="s">
         <v>83</v>
       </c>
@@ -3025,10 +3045,10 @@
       </c>
     </row>
     <row r="25" spans="2:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="B25" s="157"/>
-      <c r="C25" s="177"/>
-      <c r="D25" s="177"/>
-      <c r="E25" s="141" t="s">
+      <c r="B25" s="165"/>
+      <c r="C25" s="186"/>
+      <c r="D25" s="186"/>
+      <c r="E25" s="176" t="s">
         <v>84</v>
       </c>
       <c r="F25" s="17" t="s">
@@ -3040,15 +3060,15 @@
       <c r="H25" s="97" t="s">
         <v>187</v>
       </c>
-      <c r="I25" s="136" t="s">
+      <c r="I25" s="170" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="26" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="158"/>
-      <c r="C26" s="135"/>
-      <c r="D26" s="135"/>
-      <c r="E26" s="144"/>
+      <c r="B26" s="153"/>
+      <c r="C26" s="187"/>
+      <c r="D26" s="187"/>
+      <c r="E26" s="177"/>
       <c r="F26" s="39" t="s">
         <v>130</v>
       </c>
@@ -3056,16 +3076,16 @@
         <v>45989</v>
       </c>
       <c r="H26" s="98"/>
-      <c r="I26" s="137"/>
+      <c r="I26" s="167"/>
     </row>
     <row r="27" spans="2:9" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="176" t="s">
+      <c r="B27" s="152" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="134" t="s">
+      <c r="C27" s="185" t="s">
         <v>28</v>
       </c>
-      <c r="D27" s="134"/>
+      <c r="D27" s="185"/>
       <c r="E27" s="30" t="s">
         <v>85</v>
       </c>
@@ -3081,10 +3101,10 @@
       </c>
     </row>
     <row r="28" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="157"/>
-      <c r="C28" s="177"/>
-      <c r="D28" s="177"/>
-      <c r="E28" s="141" t="s">
+      <c r="B28" s="165"/>
+      <c r="C28" s="186"/>
+      <c r="D28" s="186"/>
+      <c r="E28" s="176" t="s">
         <v>86</v>
       </c>
       <c r="F28" s="17" t="s">
@@ -3096,15 +3116,15 @@
       <c r="H28" s="97" t="s">
         <v>187</v>
       </c>
-      <c r="I28" s="136" t="s">
+      <c r="I28" s="170" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="29" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="158"/>
-      <c r="C29" s="135"/>
-      <c r="D29" s="135"/>
-      <c r="E29" s="144"/>
+      <c r="B29" s="153"/>
+      <c r="C29" s="187"/>
+      <c r="D29" s="187"/>
+      <c r="E29" s="177"/>
       <c r="F29" s="41" t="s">
         <v>130</v>
       </c>
@@ -3112,7 +3132,7 @@
         <v>45988</v>
       </c>
       <c r="H29" s="99"/>
-      <c r="I29" s="137"/>
+      <c r="I29" s="167"/>
     </row>
     <row r="30" spans="2:9" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="32" t="s">
@@ -3173,13 +3193,13 @@
       </c>
     </row>
     <row r="33" spans="2:12" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="156">
+      <c r="B33" s="180">
         <v>2.2000000000000002</v>
       </c>
-      <c r="C33" s="145" t="s">
+      <c r="C33" s="191" t="s">
         <v>91</v>
       </c>
-      <c r="D33" s="145" t="s">
+      <c r="D33" s="191" t="s">
         <v>94</v>
       </c>
       <c r="E33" s="22" t="s">
@@ -3197,10 +3217,10 @@
       </c>
     </row>
     <row r="34" spans="2:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="B34" s="157"/>
-      <c r="C34" s="146"/>
-      <c r="D34" s="146"/>
-      <c r="E34" s="141" t="s">
+      <c r="B34" s="165"/>
+      <c r="C34" s="174"/>
+      <c r="D34" s="174"/>
+      <c r="E34" s="176" t="s">
         <v>93</v>
       </c>
       <c r="F34" s="16" t="s">
@@ -3212,15 +3232,15 @@
       <c r="H34" s="100" t="s">
         <v>190</v>
       </c>
-      <c r="I34" s="148" t="s">
+      <c r="I34" s="166" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="35" spans="2:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="B35" s="157"/>
-      <c r="C35" s="146"/>
-      <c r="D35" s="146"/>
-      <c r="E35" s="141"/>
+      <c r="B35" s="165"/>
+      <c r="C35" s="174"/>
+      <c r="D35" s="174"/>
+      <c r="E35" s="176"/>
       <c r="F35" s="16" t="s">
         <v>191</v>
       </c>
@@ -3230,13 +3250,13 @@
       <c r="H35" s="97" t="s">
         <v>192</v>
       </c>
-      <c r="I35" s="136"/>
+      <c r="I35" s="170"/>
     </row>
     <row r="36" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="186"/>
-      <c r="C36" s="154"/>
-      <c r="D36" s="154"/>
-      <c r="E36" s="183"/>
+      <c r="B36" s="181"/>
+      <c r="C36" s="184"/>
+      <c r="D36" s="184"/>
+      <c r="E36" s="192"/>
       <c r="F36" s="43" t="s">
         <v>130</v>
       </c>
@@ -3244,16 +3264,16 @@
         <v>45989</v>
       </c>
       <c r="H36" s="101"/>
-      <c r="I36" s="137"/>
+      <c r="I36" s="167"/>
     </row>
     <row r="37" spans="2:12" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="176">
+      <c r="B37" s="152">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C37" s="180" t="s">
+      <c r="C37" s="154" t="s">
         <v>30</v>
       </c>
-      <c r="D37" s="180"/>
+      <c r="D37" s="154"/>
       <c r="E37" s="30" t="s">
         <v>95</v>
       </c>
@@ -3271,10 +3291,10 @@
       </c>
     </row>
     <row r="38" spans="2:12" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="157"/>
-      <c r="C38" s="146"/>
-      <c r="D38" s="146"/>
-      <c r="E38" s="141" t="s">
+      <c r="B38" s="165"/>
+      <c r="C38" s="174"/>
+      <c r="D38" s="174"/>
+      <c r="E38" s="176" t="s">
         <v>96</v>
       </c>
       <c r="F38" s="6" t="s">
@@ -3286,15 +3306,15 @@
       <c r="H38" s="97" t="s">
         <v>129</v>
       </c>
-      <c r="I38" s="150" t="s">
+      <c r="I38" s="168" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="39" spans="2:12" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="158"/>
-      <c r="C39" s="147"/>
-      <c r="D39" s="147"/>
-      <c r="E39" s="144"/>
+      <c r="B39" s="153"/>
+      <c r="C39" s="155"/>
+      <c r="D39" s="155"/>
+      <c r="E39" s="177"/>
       <c r="F39" s="31" t="s">
         <v>130</v>
       </c>
@@ -3302,16 +3322,16 @@
         <v>45981</v>
       </c>
       <c r="H39" s="94"/>
-      <c r="I39" s="137"/>
+      <c r="I39" s="167"/>
     </row>
     <row r="40" spans="2:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="B40" s="156">
+      <c r="B40" s="180">
         <v>2.4</v>
       </c>
-      <c r="C40" s="132" t="s">
+      <c r="C40" s="215" t="s">
         <v>23</v>
       </c>
-      <c r="D40" s="145"/>
+      <c r="D40" s="191"/>
       <c r="E40" s="22" t="s">
         <v>97</v>
       </c>
@@ -3322,14 +3342,14 @@
         <v>45992</v>
       </c>
       <c r="H40" s="96"/>
-      <c r="I40" s="150" t="s">
+      <c r="I40" s="168" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="41" spans="2:12" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="186"/>
-      <c r="C41" s="178"/>
-      <c r="D41" s="154"/>
+      <c r="B41" s="181"/>
+      <c r="C41" s="216"/>
+      <c r="D41" s="184"/>
       <c r="E41" s="20" t="s">
         <v>98</v>
       </c>
@@ -3340,7 +3360,7 @@
         <v>45992</v>
       </c>
       <c r="H41" s="103"/>
-      <c r="I41" s="151"/>
+      <c r="I41" s="169"/>
     </row>
     <row r="42" spans="2:12" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="32">
@@ -3387,15 +3407,15 @@
       </c>
     </row>
     <row r="44" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="193" t="s">
+      <c r="B44" s="144" t="s">
         <v>60</v>
       </c>
-      <c r="C44" s="194"/>
-      <c r="D44" s="194"/>
-      <c r="E44" s="194"/>
-      <c r="F44" s="194"/>
-      <c r="G44" s="194"/>
-      <c r="H44" s="195"/>
+      <c r="C44" s="145"/>
+      <c r="D44" s="145"/>
+      <c r="E44" s="145"/>
+      <c r="F44" s="145"/>
+      <c r="G44" s="145"/>
+      <c r="H44" s="146"/>
       <c r="I44" s="58"/>
       <c r="L44" s="1"/>
     </row>
@@ -3432,7 +3452,7 @@
       <c r="E46" s="48" t="s">
         <v>102</v>
       </c>
-      <c r="F46" s="142" t="s">
+      <c r="F46" s="225" t="s">
         <v>185</v>
       </c>
       <c r="G46" s="51">
@@ -3454,7 +3474,7 @@
       <c r="E47" s="47" t="s">
         <v>103</v>
       </c>
-      <c r="F47" s="143"/>
+      <c r="F47" s="226"/>
       <c r="G47" s="50">
         <v>45989</v>
       </c>
@@ -3486,15 +3506,15 @@
       </c>
     </row>
     <row r="49" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="199" t="s">
+      <c r="B49" s="147" t="s">
         <v>68</v>
       </c>
-      <c r="C49" s="200"/>
-      <c r="D49" s="200"/>
-      <c r="E49" s="200"/>
-      <c r="F49" s="200"/>
-      <c r="G49" s="200"/>
-      <c r="H49" s="201"/>
+      <c r="C49" s="148"/>
+      <c r="D49" s="148"/>
+      <c r="E49" s="148"/>
+      <c r="F49" s="148"/>
+      <c r="G49" s="148"/>
+      <c r="H49" s="149"/>
       <c r="I49" s="58"/>
     </row>
     <row r="50" spans="2:12" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3565,15 +3585,15 @@
       <c r="L52"/>
     </row>
     <row r="53" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="197" t="s">
+      <c r="B53" s="150" t="s">
         <v>67</v>
       </c>
-      <c r="C53" s="198"/>
-      <c r="D53" s="198"/>
-      <c r="E53" s="198"/>
-      <c r="F53" s="198"/>
-      <c r="G53" s="198"/>
-      <c r="H53" s="198"/>
+      <c r="C53" s="151"/>
+      <c r="D53" s="151"/>
+      <c r="E53" s="151"/>
+      <c r="F53" s="151"/>
+      <c r="G53" s="151"/>
+      <c r="H53" s="151"/>
       <c r="I53" s="58"/>
       <c r="L53" s="1"/>
     </row>
@@ -3666,15 +3686,15 @@
       </c>
     </row>
     <row r="58" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="124" t="s">
+      <c r="B58" s="171" t="s">
         <v>66</v>
       </c>
-      <c r="C58" s="125"/>
-      <c r="D58" s="125"/>
-      <c r="E58" s="125"/>
-      <c r="F58" s="125"/>
-      <c r="G58" s="125"/>
-      <c r="H58" s="125"/>
+      <c r="C58" s="172"/>
+      <c r="D58" s="172"/>
+      <c r="E58" s="172"/>
+      <c r="F58" s="172"/>
+      <c r="G58" s="172"/>
+      <c r="H58" s="172"/>
       <c r="I58" s="58"/>
     </row>
     <row r="59" spans="2:12" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3700,13 +3720,13 @@
       </c>
     </row>
     <row r="60" spans="2:12" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="176">
+      <c r="B60" s="152">
         <v>6.2</v>
       </c>
-      <c r="C60" s="180" t="s">
+      <c r="C60" s="154" t="s">
         <v>16</v>
       </c>
-      <c r="D60" s="180"/>
+      <c r="D60" s="154"/>
       <c r="E60" s="69" t="s">
         <v>153</v>
       </c>
@@ -3722,10 +3742,10 @@
       </c>
     </row>
     <row r="61" spans="2:12" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="157"/>
-      <c r="C61" s="146"/>
-      <c r="D61" s="146"/>
-      <c r="E61" s="141" t="s">
+      <c r="B61" s="165"/>
+      <c r="C61" s="174"/>
+      <c r="D61" s="174"/>
+      <c r="E61" s="176" t="s">
         <v>154</v>
       </c>
       <c r="F61" s="16" t="s">
@@ -3737,15 +3757,15 @@
       <c r="H61" s="100" t="s">
         <v>162</v>
       </c>
-      <c r="I61" s="148" t="s">
+      <c r="I61" s="166" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="62" spans="2:12" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="158"/>
-      <c r="C62" s="147"/>
-      <c r="D62" s="147"/>
-      <c r="E62" s="144"/>
+      <c r="B62" s="153"/>
+      <c r="C62" s="155"/>
+      <c r="D62" s="155"/>
+      <c r="E62" s="177"/>
       <c r="F62" s="41" t="s">
         <v>130</v>
       </c>
@@ -3753,7 +3773,7 @@
         <v>45985</v>
       </c>
       <c r="H62" s="99"/>
-      <c r="I62" s="137"/>
+      <c r="I62" s="167"/>
     </row>
     <row r="63" spans="2:12" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="18">
@@ -3778,28 +3798,28 @@
       </c>
     </row>
     <row r="64" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="191" t="s">
+      <c r="B64" s="163" t="s">
         <v>65</v>
       </c>
-      <c r="C64" s="192"/>
-      <c r="D64" s="192"/>
-      <c r="E64" s="192"/>
-      <c r="F64" s="192"/>
-      <c r="G64" s="192"/>
-      <c r="H64" s="192"/>
+      <c r="C64" s="164"/>
+      <c r="D64" s="164"/>
+      <c r="E64" s="164"/>
+      <c r="F64" s="164"/>
+      <c r="G64" s="164"/>
+      <c r="H64" s="164"/>
       <c r="I64" s="58"/>
     </row>
     <row r="65" spans="2:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="176">
+      <c r="B65" s="152">
         <v>7.1</v>
       </c>
-      <c r="C65" s="180" t="s">
+      <c r="C65" s="154" t="s">
         <v>163</v>
       </c>
-      <c r="D65" s="180" t="s">
+      <c r="D65" s="154" t="s">
         <v>164</v>
       </c>
-      <c r="E65" s="149" t="s">
+      <c r="E65" s="175" t="s">
         <v>170</v>
       </c>
       <c r="F65" s="30" t="s">
@@ -3808,46 +3828,46 @@
       <c r="G65" s="38">
         <v>45985</v>
       </c>
-      <c r="H65" s="139" t="s">
+      <c r="H65" s="223" t="s">
         <v>174</v>
       </c>
-      <c r="I65" s="148" t="s">
+      <c r="I65" s="166" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="66" spans="2:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="157"/>
-      <c r="C66" s="146"/>
-      <c r="D66" s="146"/>
-      <c r="E66" s="141"/>
+      <c r="B66" s="165"/>
+      <c r="C66" s="174"/>
+      <c r="D66" s="174"/>
+      <c r="E66" s="176"/>
       <c r="F66" s="6" t="s">
         <v>171</v>
       </c>
       <c r="G66" s="11">
         <v>45985</v>
       </c>
-      <c r="H66" s="140"/>
-      <c r="I66" s="136"/>
+      <c r="H66" s="224"/>
+      <c r="I66" s="170"/>
     </row>
     <row r="67" spans="2:9" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="157"/>
-      <c r="C67" s="146"/>
-      <c r="D67" s="146"/>
-      <c r="E67" s="141"/>
+      <c r="B67" s="165"/>
+      <c r="C67" s="174"/>
+      <c r="D67" s="174"/>
+      <c r="E67" s="176"/>
       <c r="F67" s="6" t="s">
         <v>173</v>
       </c>
       <c r="G67" s="11">
         <v>45985</v>
       </c>
-      <c r="H67" s="140"/>
-      <c r="I67" s="136"/>
+      <c r="H67" s="224"/>
+      <c r="I67" s="170"/>
     </row>
     <row r="68" spans="2:9" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="158"/>
-      <c r="C68" s="147"/>
-      <c r="D68" s="147"/>
-      <c r="E68" s="144"/>
+      <c r="B68" s="153"/>
+      <c r="C68" s="155"/>
+      <c r="D68" s="155"/>
+      <c r="E68" s="177"/>
       <c r="F68" s="41" t="s">
         <v>130</v>
       </c>
@@ -3855,16 +3875,16 @@
         <v>45995</v>
       </c>
       <c r="H68" s="94"/>
-      <c r="I68" s="137"/>
+      <c r="I68" s="167"/>
     </row>
     <row r="69" spans="2:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="156">
+      <c r="B69" s="180">
         <v>7.2</v>
       </c>
-      <c r="C69" s="145" t="s">
+      <c r="C69" s="191" t="s">
         <v>17</v>
       </c>
-      <c r="D69" s="145"/>
+      <c r="D69" s="191"/>
       <c r="E69" s="28" t="s">
         <v>112</v>
       </c>
@@ -3880,10 +3900,10 @@
       </c>
     </row>
     <row r="70" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="157"/>
-      <c r="C70" s="146"/>
-      <c r="D70" s="146"/>
-      <c r="E70" s="141" t="s">
+      <c r="B70" s="165"/>
+      <c r="C70" s="174"/>
+      <c r="D70" s="174"/>
+      <c r="E70" s="176" t="s">
         <v>177</v>
       </c>
       <c r="F70" s="16" t="s">
@@ -3895,15 +3915,15 @@
       <c r="H70" s="100" t="s">
         <v>175</v>
       </c>
-      <c r="I70" s="148" t="s">
+      <c r="I70" s="166" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="71" spans="2:9" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="157"/>
-      <c r="C71" s="146"/>
-      <c r="D71" s="146"/>
-      <c r="E71" s="141"/>
+      <c r="B71" s="165"/>
+      <c r="C71" s="174"/>
+      <c r="D71" s="174"/>
+      <c r="E71" s="176"/>
       <c r="F71" s="5" t="s">
         <v>130</v>
       </c>
@@ -3911,13 +3931,13 @@
         <v>45980</v>
       </c>
       <c r="H71" s="100"/>
-      <c r="I71" s="137"/>
+      <c r="I71" s="167"/>
     </row>
     <row r="72" spans="2:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="157"/>
-      <c r="C72" s="146"/>
-      <c r="D72" s="146"/>
-      <c r="E72" s="141" t="s">
+      <c r="B72" s="165"/>
+      <c r="C72" s="174"/>
+      <c r="D72" s="174"/>
+      <c r="E72" s="176" t="s">
         <v>178</v>
       </c>
       <c r="F72" s="6" t="s">
@@ -3927,15 +3947,15 @@
       <c r="H72" s="100" t="s">
         <v>195</v>
       </c>
-      <c r="I72" s="150" t="s">
+      <c r="I72" s="168" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="73" spans="2:9" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="186"/>
-      <c r="C73" s="154"/>
-      <c r="D73" s="154"/>
-      <c r="E73" s="183"/>
+      <c r="B73" s="181"/>
+      <c r="C73" s="184"/>
+      <c r="D73" s="184"/>
+      <c r="E73" s="192"/>
       <c r="F73" s="20" t="s">
         <v>130</v>
       </c>
@@ -3943,19 +3963,19 @@
         <v>45992</v>
       </c>
       <c r="H73" s="101"/>
-      <c r="I73" s="151"/>
+      <c r="I73" s="169"/>
     </row>
     <row r="74" spans="2:9" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="176">
+      <c r="B74" s="152">
         <v>7.3</v>
       </c>
-      <c r="C74" s="180" t="s">
+      <c r="C74" s="154" t="s">
         <v>18</v>
       </c>
-      <c r="D74" s="134" t="s">
+      <c r="D74" s="185" t="s">
         <v>165</v>
       </c>
-      <c r="E74" s="196" t="s">
+      <c r="E74" s="178" t="s">
         <v>113</v>
       </c>
       <c r="F74" s="71" t="s">
@@ -3967,15 +3987,15 @@
       <c r="H74" s="107" t="s">
         <v>166</v>
       </c>
-      <c r="I74" s="148" t="s">
+      <c r="I74" s="166" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="75" spans="2:9" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="157"/>
-      <c r="C75" s="146"/>
-      <c r="D75" s="177"/>
-      <c r="E75" s="138"/>
+      <c r="B75" s="165"/>
+      <c r="C75" s="174"/>
+      <c r="D75" s="186"/>
+      <c r="E75" s="179"/>
       <c r="F75" s="9" t="s">
         <v>130</v>
       </c>
@@ -3983,13 +4003,13 @@
         <v>45933</v>
       </c>
       <c r="H75" s="100"/>
-      <c r="I75" s="151"/>
+      <c r="I75" s="169"/>
     </row>
     <row r="76" spans="2:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="157"/>
-      <c r="C76" s="146"/>
-      <c r="D76" s="177"/>
-      <c r="E76" s="138" t="s">
+      <c r="B76" s="165"/>
+      <c r="C76" s="174"/>
+      <c r="D76" s="186"/>
+      <c r="E76" s="179" t="s">
         <v>114</v>
       </c>
       <c r="F76" s="6" t="s">
@@ -4001,15 +4021,15 @@
       <c r="H76" s="100" t="s">
         <v>169</v>
       </c>
-      <c r="I76" s="148" t="s">
+      <c r="I76" s="166" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="77" spans="2:9" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="157"/>
-      <c r="C77" s="146"/>
-      <c r="D77" s="177"/>
-      <c r="E77" s="138"/>
+      <c r="B77" s="165"/>
+      <c r="C77" s="174"/>
+      <c r="D77" s="186"/>
+      <c r="E77" s="179"/>
       <c r="F77" s="8" t="s">
         <v>130</v>
       </c>
@@ -4017,12 +4037,12 @@
         <v>45967</v>
       </c>
       <c r="H77" s="74"/>
-      <c r="I77" s="137"/>
+      <c r="I77" s="167"/>
     </row>
     <row r="78" spans="2:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="158"/>
-      <c r="C78" s="147"/>
-      <c r="D78" s="135"/>
+      <c r="B78" s="153"/>
+      <c r="C78" s="155"/>
+      <c r="D78" s="187"/>
       <c r="E78" s="31" t="s">
         <v>115</v>
       </c>
@@ -4038,14 +4058,14 @@
       </c>
     </row>
     <row r="79" spans="2:9" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="176">
+      <c r="B79" s="152">
         <v>7.4</v>
       </c>
-      <c r="C79" s="180" t="s">
+      <c r="C79" s="154" t="s">
         <v>19</v>
       </c>
-      <c r="D79" s="180"/>
-      <c r="E79" s="149" t="s">
+      <c r="D79" s="154"/>
+      <c r="E79" s="175" t="s">
         <v>198</v>
       </c>
       <c r="F79" s="71" t="s">
@@ -4057,15 +4077,15 @@
       <c r="H79" s="102" t="s">
         <v>158</v>
       </c>
-      <c r="I79" s="148" t="s">
+      <c r="I79" s="166" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="80" spans="2:9" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B80" s="157"/>
-      <c r="C80" s="146"/>
-      <c r="D80" s="146"/>
-      <c r="E80" s="141"/>
+      <c r="B80" s="165"/>
+      <c r="C80" s="174"/>
+      <c r="D80" s="174"/>
+      <c r="E80" s="176"/>
       <c r="F80" s="6" t="s">
         <v>160</v>
       </c>
@@ -4075,13 +4095,13 @@
       <c r="H80" s="108" t="s">
         <v>161</v>
       </c>
-      <c r="I80" s="136"/>
+      <c r="I80" s="170"/>
     </row>
     <row r="81" spans="2:9" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="157"/>
-      <c r="C81" s="146"/>
-      <c r="D81" s="146"/>
-      <c r="E81" s="141"/>
+      <c r="B81" s="165"/>
+      <c r="C81" s="174"/>
+      <c r="D81" s="174"/>
+      <c r="E81" s="176"/>
       <c r="F81" s="6" t="s">
         <v>199</v>
       </c>
@@ -4091,13 +4111,13 @@
       <c r="H81" s="108" t="s">
         <v>200</v>
       </c>
-      <c r="I81" s="136"/>
+      <c r="I81" s="170"/>
     </row>
     <row r="82" spans="2:9" ht="57.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="157"/>
-      <c r="C82" s="146"/>
-      <c r="D82" s="146"/>
-      <c r="E82" s="141"/>
+      <c r="B82" s="165"/>
+      <c r="C82" s="174"/>
+      <c r="D82" s="174"/>
+      <c r="E82" s="176"/>
       <c r="F82" s="8" t="s">
         <v>130</v>
       </c>
@@ -4105,13 +4125,13 @@
         <v>45995</v>
       </c>
       <c r="H82" s="108"/>
-      <c r="I82" s="137"/>
+      <c r="I82" s="167"/>
     </row>
     <row r="83" spans="2:9" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="157"/>
-      <c r="C83" s="146"/>
-      <c r="D83" s="146"/>
-      <c r="E83" s="141" t="s">
+      <c r="B83" s="165"/>
+      <c r="C83" s="174"/>
+      <c r="D83" s="174"/>
+      <c r="E83" s="176" t="s">
         <v>157</v>
       </c>
       <c r="F83" s="6" t="s">
@@ -4123,15 +4143,15 @@
       <c r="H83" s="97" t="s">
         <v>156</v>
       </c>
-      <c r="I83" s="150" t="s">
+      <c r="I83" s="168" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="84" spans="2:9" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B84" s="158"/>
-      <c r="C84" s="147"/>
-      <c r="D84" s="147"/>
-      <c r="E84" s="144"/>
+      <c r="B84" s="153"/>
+      <c r="C84" s="155"/>
+      <c r="D84" s="155"/>
+      <c r="E84" s="177"/>
       <c r="F84" s="31" t="s">
         <v>130</v>
       </c>
@@ -4139,28 +4159,28 @@
         <v>45987</v>
       </c>
       <c r="H84" s="94"/>
-      <c r="I84" s="137"/>
+      <c r="I84" s="167"/>
     </row>
     <row r="85" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B85" s="193" t="s">
+      <c r="B85" s="144" t="s">
         <v>64</v>
       </c>
-      <c r="C85" s="194"/>
-      <c r="D85" s="194"/>
-      <c r="E85" s="194"/>
-      <c r="F85" s="194"/>
-      <c r="G85" s="194"/>
-      <c r="H85" s="195"/>
+      <c r="C85" s="145"/>
+      <c r="D85" s="145"/>
+      <c r="E85" s="145"/>
+      <c r="F85" s="145"/>
+      <c r="G85" s="145"/>
+      <c r="H85" s="146"/>
       <c r="I85" s="58"/>
     </row>
     <row r="86" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="176">
+      <c r="B86" s="152">
         <v>8.1</v>
       </c>
-      <c r="C86" s="180" t="s">
+      <c r="C86" s="154" t="s">
         <v>34</v>
       </c>
-      <c r="D86" s="179"/>
+      <c r="D86" s="156"/>
       <c r="E86" s="30" t="s">
         <v>179</v>
       </c>
@@ -4171,14 +4191,14 @@
         <v>45980</v>
       </c>
       <c r="H86" s="93"/>
-      <c r="I86" s="148" t="s">
+      <c r="I86" s="166" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="87" spans="2:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="157"/>
-      <c r="C87" s="146"/>
-      <c r="D87" s="160"/>
+      <c r="B87" s="165"/>
+      <c r="C87" s="174"/>
+      <c r="D87" s="182"/>
       <c r="E87" s="5" t="s">
         <v>180</v>
       </c>
@@ -4189,12 +4209,12 @@
         <v>45980</v>
       </c>
       <c r="H87" s="74"/>
-      <c r="I87" s="152"/>
+      <c r="I87" s="199"/>
     </row>
     <row r="88" spans="2:9" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B88" s="158"/>
-      <c r="C88" s="147"/>
-      <c r="D88" s="161"/>
+      <c r="B88" s="153"/>
+      <c r="C88" s="155"/>
+      <c r="D88" s="157"/>
       <c r="E88" s="31" t="s">
         <v>181</v>
       </c>
@@ -4205,16 +4225,16 @@
         <v>45980</v>
       </c>
       <c r="H88" s="94"/>
-      <c r="I88" s="153"/>
+      <c r="I88" s="200"/>
     </row>
     <row r="89" spans="2:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="B89" s="176">
+      <c r="B89" s="152">
         <v>8.1999999999999993</v>
       </c>
-      <c r="C89" s="180" t="s">
+      <c r="C89" s="154" t="s">
         <v>33</v>
       </c>
-      <c r="D89" s="179"/>
+      <c r="D89" s="156"/>
       <c r="E89" s="30" t="s">
         <v>116</v>
       </c>
@@ -4230,9 +4250,9 @@
       </c>
     </row>
     <row r="90" spans="2:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B90" s="158"/>
-      <c r="C90" s="147"/>
-      <c r="D90" s="161"/>
+      <c r="B90" s="153"/>
+      <c r="C90" s="155"/>
+      <c r="D90" s="157"/>
       <c r="E90" s="31" t="s">
         <v>117</v>
       </c>
@@ -4292,13 +4312,13 @@
       </c>
     </row>
     <row r="93" spans="2:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="B93" s="176">
+      <c r="B93" s="152">
         <v>8.5</v>
       </c>
-      <c r="C93" s="180" t="s">
+      <c r="C93" s="154" t="s">
         <v>36</v>
       </c>
-      <c r="D93" s="179"/>
+      <c r="D93" s="156"/>
       <c r="E93" s="30" t="s">
         <v>120</v>
       </c>
@@ -4314,9 +4334,9 @@
       </c>
     </row>
     <row r="94" spans="2:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="B94" s="157"/>
-      <c r="C94" s="146"/>
-      <c r="D94" s="160"/>
+      <c r="B94" s="165"/>
+      <c r="C94" s="174"/>
+      <c r="D94" s="182"/>
       <c r="E94" s="5" t="s">
         <v>121</v>
       </c>
@@ -4332,10 +4352,10 @@
       </c>
     </row>
     <row r="95" spans="2:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="B95" s="157"/>
-      <c r="C95" s="146"/>
-      <c r="D95" s="160"/>
-      <c r="E95" s="141" t="s">
+      <c r="B95" s="165"/>
+      <c r="C95" s="174"/>
+      <c r="D95" s="182"/>
+      <c r="E95" s="176" t="s">
         <v>122</v>
       </c>
       <c r="F95" s="17" t="s">
@@ -4347,15 +4367,15 @@
       <c r="H95" s="100" t="s">
         <v>184</v>
       </c>
-      <c r="I95" s="136" t="s">
+      <c r="I95" s="170" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="96" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B96" s="186"/>
-      <c r="C96" s="154"/>
-      <c r="D96" s="187"/>
-      <c r="E96" s="183"/>
+      <c r="B96" s="181"/>
+      <c r="C96" s="184"/>
+      <c r="D96" s="183"/>
+      <c r="E96" s="192"/>
       <c r="F96" s="20" t="s">
         <v>130</v>
       </c>
@@ -4363,41 +4383,41 @@
         <v>45980</v>
       </c>
       <c r="H96" s="103"/>
-      <c r="I96" s="151"/>
+      <c r="I96" s="169"/>
     </row>
     <row r="97" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B97" s="184" t="s">
+      <c r="B97" s="195" t="s">
         <v>63</v>
       </c>
-      <c r="C97" s="185"/>
-      <c r="D97" s="185"/>
-      <c r="E97" s="185"/>
-      <c r="F97" s="185"/>
-      <c r="G97" s="185"/>
-      <c r="H97" s="185"/>
+      <c r="C97" s="196"/>
+      <c r="D97" s="196"/>
+      <c r="E97" s="196"/>
+      <c r="F97" s="196"/>
+      <c r="G97" s="196"/>
+      <c r="H97" s="196"/>
       <c r="I97" s="73"/>
     </row>
     <row r="98" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B98" s="181" t="s">
+      <c r="B98" s="193" t="s">
         <v>151</v>
       </c>
-      <c r="C98" s="182"/>
-      <c r="D98" s="182"/>
-      <c r="E98" s="182"/>
-      <c r="F98" s="182"/>
-      <c r="G98" s="182"/>
+      <c r="C98" s="194"/>
+      <c r="D98" s="194"/>
+      <c r="E98" s="194"/>
+      <c r="F98" s="194"/>
+      <c r="G98" s="194"/>
       <c r="H98" s="77"/>
       <c r="I98" s="118"/>
     </row>
     <row r="99" spans="2:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="B99" s="156">
+      <c r="B99" s="180">
         <v>9.1</v>
       </c>
-      <c r="C99" s="145" t="s">
+      <c r="C99" s="191" t="s">
         <v>37</v>
       </c>
-      <c r="D99" s="159"/>
-      <c r="E99" s="162" t="s">
+      <c r="D99" s="197"/>
+      <c r="E99" s="198" t="s">
         <v>124</v>
       </c>
       <c r="F99" s="75" t="s">
@@ -4409,15 +4429,15 @@
       <c r="H99" s="96" t="s">
         <v>141</v>
       </c>
-      <c r="I99" s="150" t="s">
+      <c r="I99" s="168" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="100" spans="2:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="B100" s="157"/>
-      <c r="C100" s="146"/>
-      <c r="D100" s="160"/>
-      <c r="E100" s="141"/>
+      <c r="B100" s="165"/>
+      <c r="C100" s="174"/>
+      <c r="D100" s="182"/>
+      <c r="E100" s="176"/>
       <c r="F100" s="8" t="s">
         <v>140</v>
       </c>
@@ -4425,13 +4445,13 @@
         <v>45985</v>
       </c>
       <c r="H100" s="74"/>
-      <c r="I100" s="136"/>
+      <c r="I100" s="170"/>
     </row>
     <row r="101" spans="2:9" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B101" s="157"/>
-      <c r="C101" s="146"/>
-      <c r="D101" s="160"/>
-      <c r="E101" s="141" t="s">
+      <c r="B101" s="165"/>
+      <c r="C101" s="174"/>
+      <c r="D101" s="182"/>
+      <c r="E101" s="176" t="s">
         <v>125</v>
       </c>
       <c r="F101" s="6" t="s">
@@ -4443,15 +4463,15 @@
       <c r="H101" s="97" t="s">
         <v>139</v>
       </c>
-      <c r="I101" s="136" t="s">
+      <c r="I101" s="170" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="102" spans="2:9" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B102" s="158"/>
-      <c r="C102" s="147"/>
-      <c r="D102" s="161"/>
-      <c r="E102" s="144"/>
+      <c r="B102" s="153"/>
+      <c r="C102" s="155"/>
+      <c r="D102" s="157"/>
+      <c r="E102" s="177"/>
       <c r="F102" s="31" t="s">
         <v>138</v>
       </c>
@@ -4459,7 +4479,7 @@
         <v>45985</v>
       </c>
       <c r="H102" s="98"/>
-      <c r="I102" s="137"/>
+      <c r="I102" s="167"/>
     </row>
     <row r="103" spans="2:9" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B103" s="18">
@@ -4484,14 +4504,14 @@
       </c>
     </row>
     <row r="104" spans="2:9" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B104" s="176">
+      <c r="B104" s="152">
         <v>9.3000000000000007</v>
       </c>
-      <c r="C104" s="180" t="s">
+      <c r="C104" s="154" t="s">
         <v>39</v>
       </c>
-      <c r="D104" s="179"/>
-      <c r="E104" s="149" t="s">
+      <c r="D104" s="156"/>
+      <c r="E104" s="175" t="s">
         <v>142</v>
       </c>
       <c r="F104" s="71" t="s">
@@ -4503,67 +4523,67 @@
       <c r="H104" s="102" t="s">
         <v>144</v>
       </c>
-      <c r="I104" s="148" t="s">
+      <c r="I104" s="166" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="105" spans="2:9" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B105" s="186"/>
-      <c r="C105" s="154"/>
-      <c r="D105" s="187"/>
-      <c r="E105" s="183"/>
-      <c r="F105" s="206" t="s">
+      <c r="B105" s="181"/>
+      <c r="C105" s="184"/>
+      <c r="D105" s="183"/>
+      <c r="E105" s="192"/>
+      <c r="F105" s="125" t="s">
         <v>145</v>
       </c>
       <c r="G105" s="44">
         <v>45982</v>
       </c>
       <c r="H105" s="103"/>
-      <c r="I105" s="151"/>
+      <c r="I105" s="169"/>
     </row>
     <row r="106" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B106" s="176">
+      <c r="B106" s="152">
         <v>9.4</v>
       </c>
-      <c r="C106" s="180" t="s">
+      <c r="C106" s="154" t="s">
         <v>40</v>
       </c>
-      <c r="D106" s="179"/>
-      <c r="E106" s="210" t="s">
+      <c r="D106" s="156"/>
+      <c r="E106" s="158" t="s">
         <v>127</v>
       </c>
-      <c r="F106" s="211" t="s">
+      <c r="F106" s="127" t="s">
         <v>146</v>
       </c>
       <c r="G106" s="38">
         <v>45982</v>
       </c>
-      <c r="H106" s="215" t="s">
+      <c r="H106" s="161" t="s">
         <v>217</v>
       </c>
-      <c r="I106" s="217" t="s">
+      <c r="I106" s="133" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="107" spans="2:9" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B107" s="213"/>
-      <c r="C107" s="203"/>
-      <c r="D107" s="204"/>
-      <c r="E107" s="205"/>
-      <c r="F107" s="214" t="s">
+      <c r="B107" s="136"/>
+      <c r="C107" s="138"/>
+      <c r="D107" s="140"/>
+      <c r="E107" s="159"/>
+      <c r="F107" s="128" t="s">
         <v>218</v>
       </c>
       <c r="G107" s="57">
         <v>46030</v>
       </c>
-      <c r="H107" s="216"/>
-      <c r="I107" s="218"/>
+      <c r="H107" s="162"/>
+      <c r="I107" s="134"/>
     </row>
     <row r="108" spans="2:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B108" s="158"/>
-      <c r="C108" s="147"/>
-      <c r="D108" s="161"/>
-      <c r="E108" s="212"/>
+      <c r="B108" s="153"/>
+      <c r="C108" s="155"/>
+      <c r="D108" s="157"/>
+      <c r="E108" s="160"/>
       <c r="F108" s="72" t="s">
         <v>130</v>
       </c>
@@ -4571,19 +4591,19 @@
         <v>46031</v>
       </c>
       <c r="H108" s="94"/>
-      <c r="I108" s="219"/>
+      <c r="I108" s="135"/>
     </row>
     <row r="109" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B109" s="207" t="s">
+      <c r="B109" s="142" t="s">
         <v>62</v>
       </c>
-      <c r="C109" s="208"/>
-      <c r="D109" s="208"/>
-      <c r="E109" s="208"/>
-      <c r="F109" s="208"/>
-      <c r="G109" s="208"/>
-      <c r="H109" s="208"/>
-      <c r="I109" s="209"/>
+      <c r="C109" s="143"/>
+      <c r="D109" s="143"/>
+      <c r="E109" s="143"/>
+      <c r="F109" s="143"/>
+      <c r="G109" s="143"/>
+      <c r="H109" s="143"/>
+      <c r="I109" s="126"/>
     </row>
     <row r="110" spans="2:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B110" s="32">
@@ -4602,7 +4622,7 @@
       <c r="G110" s="36">
         <v>46009</v>
       </c>
-      <c r="H110" s="225"/>
+      <c r="H110" s="131"/>
       <c r="I110" s="113" t="s">
         <v>131</v>
       </c>
@@ -4624,7 +4644,7 @@
       <c r="G111" s="36">
         <v>46009</v>
       </c>
-      <c r="H111" s="225"/>
+      <c r="H111" s="131"/>
       <c r="I111" s="112" t="s">
         <v>131</v>
       </c>
@@ -4636,28 +4656,28 @@
       <c r="C112" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="D112" s="202" t="s">
+      <c r="D112" s="124" t="s">
         <v>215</v>
       </c>
-      <c r="E112" s="202" t="s">
+      <c r="E112" s="124" t="s">
         <v>216</v>
       </c>
-      <c r="F112" s="224"/>
-      <c r="G112" s="226"/>
+      <c r="F112" s="130"/>
+      <c r="G112" s="132"/>
       <c r="H112" s="106"/>
-      <c r="I112" s="220"/>
+      <c r="I112" s="129"/>
     </row>
     <row r="113" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B113" s="124" t="s">
+      <c r="B113" s="171" t="s">
         <v>61</v>
       </c>
-      <c r="C113" s="125"/>
-      <c r="D113" s="125"/>
-      <c r="E113" s="125"/>
-      <c r="F113" s="125"/>
-      <c r="G113" s="125"/>
-      <c r="H113" s="125"/>
-      <c r="I113" s="126"/>
+      <c r="C113" s="172"/>
+      <c r="D113" s="172"/>
+      <c r="E113" s="172"/>
+      <c r="F113" s="172"/>
+      <c r="G113" s="172"/>
+      <c r="H113" s="172"/>
+      <c r="I113" s="173"/>
     </row>
     <row r="114" spans="2:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B114" s="32">
@@ -4726,76 +4746,156 @@
       </c>
     </row>
     <row r="117" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B117" s="124" t="s">
+      <c r="B117" s="171" t="s">
         <v>208</v>
       </c>
-      <c r="C117" s="125"/>
-      <c r="D117" s="125"/>
-      <c r="E117" s="125"/>
-      <c r="F117" s="125"/>
-      <c r="G117" s="125"/>
-      <c r="H117" s="125"/>
-      <c r="I117" s="126"/>
-    </row>
-    <row r="118" spans="2:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B118" s="213">
+      <c r="C117" s="172"/>
+      <c r="D117" s="172"/>
+      <c r="E117" s="172"/>
+      <c r="F117" s="172"/>
+      <c r="G117" s="172"/>
+      <c r="H117" s="172"/>
+      <c r="I117" s="173"/>
+    </row>
+    <row r="118" spans="2:9" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B118" s="136">
         <v>12.1</v>
       </c>
-      <c r="C118" s="203" t="s">
+      <c r="C118" s="138" t="s">
         <v>209</v>
       </c>
-      <c r="D118" s="204"/>
-      <c r="E118" s="22" t="s">
+      <c r="D118" s="140"/>
+      <c r="E118" s="227" t="s">
         <v>219</v>
       </c>
-      <c r="F118" s="42" t="s">
-        <v>130</v>
+      <c r="F118" s="229" t="s">
+        <v>221</v>
       </c>
       <c r="G118" s="29">
         <v>46028</v>
       </c>
-      <c r="H118" s="96"/>
+      <c r="H118" s="230" t="s">
+        <v>222</v>
+      </c>
       <c r="I118" s="112" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="119" spans="2:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B119" s="221"/>
-      <c r="C119" s="222"/>
-      <c r="D119" s="223"/>
-      <c r="E119" s="68" t="s">
+    <row r="119" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B119" s="136"/>
+      <c r="C119" s="138"/>
+      <c r="D119" s="140"/>
+      <c r="E119" s="228"/>
+      <c r="F119" s="42" t="s">
+        <v>130</v>
+      </c>
+      <c r="G119" s="29">
+        <v>46028</v>
+      </c>
+      <c r="H119" s="74"/>
+      <c r="I119" s="112"/>
+    </row>
+    <row r="120" spans="2:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B120" s="137"/>
+      <c r="C120" s="139"/>
+      <c r="D120" s="141"/>
+      <c r="E120" s="68" t="s">
         <v>220</v>
       </c>
-      <c r="F119" s="53" t="s">
-        <v>130</v>
-      </c>
-      <c r="G119" s="62">
+      <c r="F120" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="G120" s="62">
         <v>46028</v>
       </c>
-      <c r="H119" s="105"/>
-      <c r="I119" s="112" t="s">
+      <c r="H120" s="105"/>
+      <c r="I120" s="112" t="s">
         <v>131</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="128">
-    <mergeCell ref="I106:I108"/>
-    <mergeCell ref="B118:B119"/>
-    <mergeCell ref="C118:C119"/>
-    <mergeCell ref="D118:D119"/>
-    <mergeCell ref="B109:H109"/>
-    <mergeCell ref="B44:H44"/>
-    <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B53:H53"/>
-    <mergeCell ref="B106:B108"/>
-    <mergeCell ref="C106:C108"/>
-    <mergeCell ref="D106:D108"/>
-    <mergeCell ref="E106:E108"/>
-    <mergeCell ref="H106:H107"/>
-    <mergeCell ref="B64:H64"/>
-    <mergeCell ref="B85:H85"/>
-    <mergeCell ref="B74:B78"/>
-    <mergeCell ref="B79:B84"/>
+  <mergeCells count="129">
+    <mergeCell ref="E118:E119"/>
+    <mergeCell ref="B117:I117"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="I38:I39"/>
+    <mergeCell ref="E76:E77"/>
+    <mergeCell ref="H65:H67"/>
+    <mergeCell ref="E70:E71"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="I65:I68"/>
+    <mergeCell ref="E79:E82"/>
+    <mergeCell ref="I79:I82"/>
+    <mergeCell ref="I19:I21"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="I34:I36"/>
+    <mergeCell ref="I70:I71"/>
+    <mergeCell ref="I72:I73"/>
+    <mergeCell ref="I74:I75"/>
+    <mergeCell ref="I86:I88"/>
+    <mergeCell ref="D69:D73"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="D9:D12"/>
+    <mergeCell ref="E9:E12"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="G9:G12"/>
+    <mergeCell ref="H9:H12"/>
+    <mergeCell ref="F9:F12"/>
+    <mergeCell ref="I9:I12"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="B93:B96"/>
+    <mergeCell ref="I104:I105"/>
+    <mergeCell ref="B99:B102"/>
+    <mergeCell ref="C99:C102"/>
+    <mergeCell ref="D99:D102"/>
+    <mergeCell ref="E101:E102"/>
+    <mergeCell ref="E99:E100"/>
+    <mergeCell ref="I99:I100"/>
+    <mergeCell ref="I101:I102"/>
+    <mergeCell ref="D104:D105"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="B86:B88"/>
+    <mergeCell ref="C74:C78"/>
+    <mergeCell ref="D74:D78"/>
+    <mergeCell ref="D79:D84"/>
+    <mergeCell ref="C79:C84"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C33:C36"/>
+    <mergeCell ref="D33:D36"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="D86:D88"/>
+    <mergeCell ref="C69:C73"/>
+    <mergeCell ref="C86:C88"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="B58:H58"/>
     <mergeCell ref="I15:I16"/>
     <mergeCell ref="I40:I41"/>
     <mergeCell ref="I61:I62"/>
@@ -4820,26 +4920,23 @@
     <mergeCell ref="D93:D96"/>
     <mergeCell ref="C93:C96"/>
     <mergeCell ref="I76:I77"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="D27:D29"/>
-    <mergeCell ref="B31:H31"/>
-    <mergeCell ref="B86:B88"/>
-    <mergeCell ref="C74:C78"/>
-    <mergeCell ref="D74:D78"/>
-    <mergeCell ref="D79:D84"/>
-    <mergeCell ref="C79:C84"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C33:C36"/>
-    <mergeCell ref="D33:D36"/>
-    <mergeCell ref="B33:B36"/>
-    <mergeCell ref="E34:E36"/>
-    <mergeCell ref="D86:D88"/>
-    <mergeCell ref="C69:C73"/>
-    <mergeCell ref="C86:C88"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="I106:I108"/>
+    <mergeCell ref="B118:B120"/>
+    <mergeCell ref="C118:C120"/>
+    <mergeCell ref="D118:D120"/>
+    <mergeCell ref="B109:H109"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="B49:H49"/>
+    <mergeCell ref="B53:H53"/>
+    <mergeCell ref="B106:B108"/>
+    <mergeCell ref="C106:C108"/>
+    <mergeCell ref="D106:D108"/>
+    <mergeCell ref="E106:E108"/>
+    <mergeCell ref="H106:H107"/>
+    <mergeCell ref="B64:H64"/>
+    <mergeCell ref="B85:H85"/>
+    <mergeCell ref="B74:B78"/>
+    <mergeCell ref="B79:B84"/>
     <mergeCell ref="B98:G98"/>
     <mergeCell ref="B104:B105"/>
     <mergeCell ref="E104:E105"/>
@@ -4847,66 +4944,6 @@
     <mergeCell ref="D89:D90"/>
     <mergeCell ref="C89:C90"/>
     <mergeCell ref="B97:H97"/>
-    <mergeCell ref="B89:B90"/>
-    <mergeCell ref="B93:B96"/>
-    <mergeCell ref="I104:I105"/>
-    <mergeCell ref="B99:B102"/>
-    <mergeCell ref="C99:C102"/>
-    <mergeCell ref="D99:D102"/>
-    <mergeCell ref="E101:E102"/>
-    <mergeCell ref="E99:E100"/>
-    <mergeCell ref="I99:I100"/>
-    <mergeCell ref="I101:I102"/>
-    <mergeCell ref="D104:D105"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="I86:I88"/>
-    <mergeCell ref="D69:D73"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="D9:D12"/>
-    <mergeCell ref="E9:E12"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="G9:G12"/>
-    <mergeCell ref="H9:H12"/>
-    <mergeCell ref="F9:F12"/>
-    <mergeCell ref="I9:I12"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="B117:I117"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="I38:I39"/>
-    <mergeCell ref="E76:E77"/>
-    <mergeCell ref="H65:H67"/>
-    <mergeCell ref="E70:E71"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="I65:I68"/>
-    <mergeCell ref="E79:E82"/>
-    <mergeCell ref="I79:I82"/>
-    <mergeCell ref="I19:I21"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="I34:I36"/>
-    <mergeCell ref="I70:I71"/>
-    <mergeCell ref="I72:I73"/>
-    <mergeCell ref="I74:I75"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Documentation/SRS_HVPSU_Test_Results.xlsx
+++ b/Documentation/SRS_HVPSU_Test_Results.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\home\jek48386\repos\SRS300\Documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\home\jek48386\repos\srs-ps300series\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{442D95D0-0ED6-48A2-B7EC-ED21C98754DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EDDBF9B-86A4-4524-8AFF-84DF6E2A5F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1875" windowWidth="29040" windowHeight="15720" xr2:uid="{ABB50434-DF5E-4618-8107-94BD17379F73}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{ABB50434-DF5E-4618-8107-94BD17379F73}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="233">
   <si>
     <t>Test</t>
   </si>
@@ -817,9 +817,6 @@
   <si>
     <t>Pauses for 1.45 seconds 
 after being set to give time for value to stabilize before being read</t>
-  </si>
-  <si>
-    <t>12.0. Deployment</t>
   </si>
   <si>
     <t>IOC is able to be deployed</t>
@@ -889,6 +886,40 @@
   <si>
     <t>Prefix contained a colon which
  caused an error so it was removed and put into the PV name instead, Prefix was in two parts "$(P)$(R)" which caused some issues so it was changed to "$(DEVICE)"</t>
+  </si>
+  <si>
+    <t>Data on output voltage, output current and trip events are archived for data management</t>
+  </si>
+  <si>
+    <t>Run IOC, change values of the PVs and check they are archived correctly.</t>
+  </si>
+  <si>
+    <t>12.0. Deployment, archiver and device nickname</t>
+  </si>
+  <si>
+    <t>Restart IOC and check nickname is restored</t>
+  </si>
+  <si>
+    <t>Scientists are able to give the device a "friendly name" which is saved even after restarting the IOC.</t>
+  </si>
+  <si>
+    <t>Set a nickname for the device and ensure it is displayed correctly on the ui.</t>
+  </si>
+  <si>
+    <t>Start the IOC without a nickname, ensure it has a default nickname displayed.</t>
+  </si>
+  <si>
+    <t>A PV accurately monitors 
+whether output voltage and target voltage are equal (within tolerance)</t>
+  </si>
+  <si>
+    <t>Compare camonitor of voltage, target voltage and the PV. Set target to within tolerance of output voltage.</t>
+  </si>
+  <si>
+    <t>Compare camonitor of voltage, target voltage and the PV. Set target to exactly equal to output voltage.</t>
+  </si>
+  <si>
+    <t>Compare camonitor of voltage, target voltage and the PV. Set target to outside of tolerance of output voltage.</t>
   </si>
 </sst>
 </file>
@@ -1012,7 +1043,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="52">
+  <borders count="53">
     <border>
       <left/>
       <right/>
@@ -1669,11 +1700,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="231">
+  <cellXfs count="244">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2008,6 +2054,207 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2046,24 +2293,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -2085,90 +2314,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -2181,107 +2326,45 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2629,67 +2712,67 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A62839A-462D-4B14-AC2D-C7655127CCDA}">
-  <dimension ref="A1:M120"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M127"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="29.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="30.140625" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" style="10" customWidth="1"/>
-    <col min="8" max="8" width="27.5703125" customWidth="1"/>
-    <col min="9" max="9" width="6.5703125" customWidth="1"/>
-    <col min="11" max="11" width="6.42578125" customWidth="1"/>
-    <col min="12" max="12" width="24.7109375" customWidth="1"/>
-    <col min="13" max="13" width="12.28515625" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="29.5546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="30.109375" customWidth="1"/>
+    <col min="7" max="7" width="11.88671875" style="10" customWidth="1"/>
+    <col min="8" max="8" width="27.5546875" customWidth="1"/>
+    <col min="9" max="9" width="6.5546875" customWidth="1"/>
+    <col min="11" max="11" width="6.44140625" customWidth="1"/>
+    <col min="12" max="12" width="24.6640625" customWidth="1"/>
+    <col min="13" max="13" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="217" t="s">
-        <v>211</v>
-      </c>
-      <c r="B1" s="218"/>
+    <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="141" t="s">
+        <v>210</v>
+      </c>
+      <c r="B1" s="142"/>
       <c r="C1" s="122"/>
       <c r="D1" s="123"/>
       <c r="E1" s="121"/>
       <c r="F1" s="121"/>
     </row>
-    <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="219" t="s">
-        <v>210</v>
-      </c>
-      <c r="B2" s="220"/>
-      <c r="C2" s="220"/>
-      <c r="D2" s="220"/>
-      <c r="E2" s="221"/>
+    <row r="2" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="143" t="s">
+        <v>209</v>
+      </c>
+      <c r="B2" s="144"/>
+      <c r="C2" s="144"/>
+      <c r="D2" s="144"/>
+      <c r="E2" s="145"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="215" t="s">
-        <v>212</v>
-      </c>
-      <c r="B3" s="222"/>
-      <c r="C3" s="222"/>
-      <c r="D3" s="222"/>
-      <c r="E3" s="222"/>
+    <row r="3" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="146" t="s">
+        <v>211</v>
+      </c>
+      <c r="B3" s="147"/>
+      <c r="C3" s="147"/>
+      <c r="D3" s="147"/>
+      <c r="E3" s="147"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C4" s="120"/>
       <c r="D4" s="120"/>
       <c r="E4" s="120"/>
       <c r="F4" s="120"/>
       <c r="G4" s="120"/>
     </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:13" s="4" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="202" t="s">
+    <row r="5" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="1:13" s="4" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="175" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="203"/>
+      <c r="C6" s="176"/>
       <c r="D6" s="24" t="s">
         <v>206</v>
       </c>
@@ -2708,28 +2791,28 @@
       <c r="I6" s="86" t="s">
         <v>132</v>
       </c>
-      <c r="K6" s="201" t="s">
+      <c r="K6" s="167" t="s">
         <v>147</v>
       </c>
-      <c r="L6" s="201"/>
-    </row>
-    <row r="7" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="204" t="s">
+      <c r="L6" s="167"/>
+    </row>
+    <row r="7" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="177" t="s">
         <v>59</v>
       </c>
-      <c r="C7" s="205"/>
-      <c r="D7" s="205"/>
-      <c r="E7" s="205"/>
-      <c r="F7" s="205"/>
-      <c r="G7" s="205"/>
-      <c r="H7" s="205"/>
+      <c r="C7" s="178"/>
+      <c r="D7" s="178"/>
+      <c r="E7" s="178"/>
+      <c r="F7" s="178"/>
+      <c r="G7" s="178"/>
+      <c r="H7" s="178"/>
       <c r="I7" s="91"/>
       <c r="K7" s="13"/>
       <c r="L7" s="3" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="87" t="s">
         <v>57</v>
       </c>
@@ -2747,25 +2830,25 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="180" t="s">
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="168" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="191" t="s">
+      <c r="C9" s="157" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="197"/>
-      <c r="E9" s="198" t="s">
+      <c r="D9" s="171"/>
+      <c r="E9" s="174" t="s">
         <v>69</v>
       </c>
-      <c r="F9" s="212" t="s">
-        <v>130</v>
-      </c>
-      <c r="G9" s="206">
+      <c r="F9" s="185" t="s">
+        <v>130</v>
+      </c>
+      <c r="G9" s="179">
         <v>45992</v>
       </c>
-      <c r="H9" s="209"/>
-      <c r="I9" s="166" t="s">
+      <c r="H9" s="182"/>
+      <c r="I9" s="161" t="s">
         <v>131</v>
       </c>
       <c r="K9" s="15"/>
@@ -2773,42 +2856,42 @@
         <v>150</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="165"/>
-      <c r="C10" s="174"/>
-      <c r="D10" s="182"/>
-      <c r="E10" s="176"/>
-      <c r="F10" s="213"/>
-      <c r="G10" s="207"/>
-      <c r="H10" s="210"/>
-      <c r="I10" s="170"/>
+    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="169"/>
+      <c r="C10" s="158"/>
+      <c r="D10" s="172"/>
+      <c r="E10" s="155"/>
+      <c r="F10" s="186"/>
+      <c r="G10" s="180"/>
+      <c r="H10" s="183"/>
+      <c r="I10" s="160"/>
       <c r="K10" s="19"/>
       <c r="L10" s="2" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="165"/>
-      <c r="C11" s="174"/>
-      <c r="D11" s="182"/>
-      <c r="E11" s="176"/>
-      <c r="F11" s="213"/>
-      <c r="G11" s="207"/>
-      <c r="H11" s="210"/>
-      <c r="I11" s="170"/>
-    </row>
-    <row r="12" spans="1:13" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="153"/>
-      <c r="C12" s="155"/>
-      <c r="D12" s="157"/>
-      <c r="E12" s="177"/>
-      <c r="F12" s="214"/>
-      <c r="G12" s="208"/>
-      <c r="H12" s="211"/>
-      <c r="I12" s="167"/>
+    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="169"/>
+      <c r="C11" s="158"/>
+      <c r="D11" s="172"/>
+      <c r="E11" s="155"/>
+      <c r="F11" s="186"/>
+      <c r="G11" s="180"/>
+      <c r="H11" s="183"/>
+      <c r="I11" s="160"/>
+    </row>
+    <row r="12" spans="1:13" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="170"/>
+      <c r="C12" s="159"/>
+      <c r="D12" s="173"/>
+      <c r="E12" s="156"/>
+      <c r="F12" s="187"/>
+      <c r="G12" s="181"/>
+      <c r="H12" s="184"/>
+      <c r="I12" s="151"/>
       <c r="M12" s="12"/>
     </row>
-    <row r="13" spans="1:13" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="32" t="s">
         <v>49</v>
       </c>
@@ -2830,7 +2913,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="32" t="s">
         <v>50</v>
       </c>
@@ -2852,14 +2935,14 @@
         <v>131</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="152" t="s">
+    <row r="15" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="188" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="185" t="s">
+      <c r="C15" s="148" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="185" t="s">
+      <c r="D15" s="148" t="s">
         <v>73</v>
       </c>
       <c r="E15" s="37" t="s">
@@ -2872,14 +2955,14 @@
         <v>45989</v>
       </c>
       <c r="H15" s="93"/>
-      <c r="I15" s="166" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="153"/>
-      <c r="C16" s="187"/>
-      <c r="D16" s="187"/>
+      <c r="I15" s="161" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="170"/>
+      <c r="C16" s="149"/>
+      <c r="D16" s="149"/>
       <c r="E16" s="31" t="s">
         <v>74</v>
       </c>
@@ -2890,9 +2973,9 @@
         <v>45989</v>
       </c>
       <c r="H16" s="94"/>
-      <c r="I16" s="167"/>
-    </row>
-    <row r="17" spans="2:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I16" s="151"/>
+    </row>
+    <row r="17" spans="2:9" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="63" t="s">
         <v>52</v>
       </c>
@@ -2916,7 +2999,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="18" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="80">
         <v>1.1000000000000001</v>
       </c>
@@ -2930,14 +3013,14 @@
       <c r="H18" s="76"/>
       <c r="I18" s="85"/>
     </row>
-    <row r="19" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="180" t="s">
+    <row r="19" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="168" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="215" t="s">
+      <c r="C19" s="146" t="s">
         <v>79</v>
       </c>
-      <c r="D19" s="191"/>
+      <c r="D19" s="157"/>
       <c r="E19" s="22" t="s">
         <v>77</v>
       </c>
@@ -2948,14 +3031,14 @@
         <v>45992</v>
       </c>
       <c r="H19" s="96"/>
-      <c r="I19" s="168" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="165"/>
-      <c r="C20" s="186"/>
-      <c r="D20" s="174"/>
+      <c r="I19" s="150" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="169"/>
+      <c r="C20" s="189"/>
+      <c r="D20" s="158"/>
       <c r="E20" s="5" t="s">
         <v>78</v>
       </c>
@@ -2966,12 +3049,12 @@
         <v>45992</v>
       </c>
       <c r="H20" s="74"/>
-      <c r="I20" s="170"/>
-    </row>
-    <row r="21" spans="2:9" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="153"/>
-      <c r="C21" s="187"/>
-      <c r="D21" s="155"/>
+      <c r="I20" s="160"/>
+    </row>
+    <row r="21" spans="2:9" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="170"/>
+      <c r="C21" s="149"/>
+      <c r="D21" s="159"/>
       <c r="E21" s="31" t="s">
         <v>80</v>
       </c>
@@ -2982,16 +3065,16 @@
         <v>45992</v>
       </c>
       <c r="H21" s="94"/>
-      <c r="I21" s="167"/>
-    </row>
-    <row r="22" spans="2:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="B22" s="152" t="s">
+      <c r="I21" s="151"/>
+    </row>
+    <row r="22" spans="2:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B22" s="188" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="185" t="s">
+      <c r="C22" s="148" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="185"/>
+      <c r="D22" s="148"/>
       <c r="E22" s="30" t="s">
         <v>81</v>
       </c>
@@ -3002,14 +3085,14 @@
         <v>45992</v>
       </c>
       <c r="H22" s="93"/>
-      <c r="I22" s="166" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="153"/>
-      <c r="C23" s="187"/>
-      <c r="D23" s="187"/>
+      <c r="I22" s="161" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="170"/>
+      <c r="C23" s="149"/>
+      <c r="D23" s="149"/>
       <c r="E23" s="31" t="s">
         <v>82</v>
       </c>
@@ -3020,16 +3103,16 @@
         <v>45992</v>
       </c>
       <c r="H23" s="94"/>
-      <c r="I23" s="167"/>
-    </row>
-    <row r="24" spans="2:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="B24" s="152" t="s">
+      <c r="I23" s="151"/>
+    </row>
+    <row r="24" spans="2:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B24" s="188" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="185" t="s">
+      <c r="C24" s="148" t="s">
         <v>27</v>
       </c>
-      <c r="D24" s="185"/>
+      <c r="D24" s="148"/>
       <c r="E24" s="30" t="s">
         <v>83</v>
       </c>
@@ -3044,11 +3127,11 @@
         <v>131</v>
       </c>
     </row>
-    <row r="25" spans="2:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="B25" s="165"/>
-      <c r="C25" s="186"/>
-      <c r="D25" s="186"/>
-      <c r="E25" s="176" t="s">
+    <row r="25" spans="2:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B25" s="169"/>
+      <c r="C25" s="189"/>
+      <c r="D25" s="189"/>
+      <c r="E25" s="155" t="s">
         <v>84</v>
       </c>
       <c r="F25" s="17" t="s">
@@ -3060,15 +3143,15 @@
       <c r="H25" s="97" t="s">
         <v>187</v>
       </c>
-      <c r="I25" s="170" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="153"/>
-      <c r="C26" s="187"/>
-      <c r="D26" s="187"/>
-      <c r="E26" s="177"/>
+      <c r="I25" s="160" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="170"/>
+      <c r="C26" s="149"/>
+      <c r="D26" s="149"/>
+      <c r="E26" s="156"/>
       <c r="F26" s="39" t="s">
         <v>130</v>
       </c>
@@ -3076,16 +3159,16 @@
         <v>45989</v>
       </c>
       <c r="H26" s="98"/>
-      <c r="I26" s="167"/>
-    </row>
-    <row r="27" spans="2:9" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="152" t="s">
+      <c r="I26" s="151"/>
+    </row>
+    <row r="27" spans="2:9" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="188" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="185" t="s">
+      <c r="C27" s="148" t="s">
         <v>28</v>
       </c>
-      <c r="D27" s="185"/>
+      <c r="D27" s="148"/>
       <c r="E27" s="30" t="s">
         <v>85</v>
       </c>
@@ -3100,11 +3183,11 @@
         <v>131</v>
       </c>
     </row>
-    <row r="28" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="165"/>
-      <c r="C28" s="186"/>
-      <c r="D28" s="186"/>
-      <c r="E28" s="176" t="s">
+    <row r="28" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="169"/>
+      <c r="C28" s="189"/>
+      <c r="D28" s="189"/>
+      <c r="E28" s="155" t="s">
         <v>86</v>
       </c>
       <c r="F28" s="17" t="s">
@@ -3116,15 +3199,15 @@
       <c r="H28" s="97" t="s">
         <v>187</v>
       </c>
-      <c r="I28" s="170" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="153"/>
-      <c r="C29" s="187"/>
-      <c r="D29" s="187"/>
-      <c r="E29" s="177"/>
+      <c r="I28" s="160" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="170"/>
+      <c r="C29" s="149"/>
+      <c r="D29" s="149"/>
+      <c r="E29" s="156"/>
       <c r="F29" s="41" t="s">
         <v>130</v>
       </c>
@@ -3132,9 +3215,9 @@
         <v>45988</v>
       </c>
       <c r="H29" s="99"/>
-      <c r="I29" s="167"/>
-    </row>
-    <row r="30" spans="2:9" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I29" s="151"/>
+    </row>
+    <row r="30" spans="2:9" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B30" s="32" t="s">
         <v>56</v>
       </c>
@@ -3158,19 +3241,19 @@
         <v>131</v>
       </c>
     </row>
-    <row r="31" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="188" t="s">
+    <row r="31" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="195" t="s">
         <v>58</v>
       </c>
-      <c r="C31" s="189"/>
-      <c r="D31" s="189"/>
-      <c r="E31" s="189"/>
-      <c r="F31" s="189"/>
-      <c r="G31" s="189"/>
-      <c r="H31" s="190"/>
+      <c r="C31" s="196"/>
+      <c r="D31" s="196"/>
+      <c r="E31" s="196"/>
+      <c r="F31" s="196"/>
+      <c r="G31" s="196"/>
+      <c r="H31" s="197"/>
       <c r="I31" s="58"/>
     </row>
-    <row r="32" spans="2:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:9" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B32" s="32">
         <v>2.1</v>
       </c>
@@ -3192,14 +3275,14 @@
         <v>131</v>
       </c>
     </row>
-    <row r="33" spans="2:12" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="180">
+    <row r="33" spans="2:12" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="168">
         <v>2.2000000000000002</v>
       </c>
-      <c r="C33" s="191" t="s">
+      <c r="C33" s="157" t="s">
         <v>91</v>
       </c>
-      <c r="D33" s="191" t="s">
+      <c r="D33" s="157" t="s">
         <v>94</v>
       </c>
       <c r="E33" s="22" t="s">
@@ -3216,11 +3299,11 @@
         <v>131</v>
       </c>
     </row>
-    <row r="34" spans="2:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="B34" s="165"/>
-      <c r="C34" s="174"/>
-      <c r="D34" s="174"/>
-      <c r="E34" s="176" t="s">
+    <row r="34" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B34" s="169"/>
+      <c r="C34" s="158"/>
+      <c r="D34" s="158"/>
+      <c r="E34" s="155" t="s">
         <v>93</v>
       </c>
       <c r="F34" s="16" t="s">
@@ -3232,15 +3315,15 @@
       <c r="H34" s="100" t="s">
         <v>190</v>
       </c>
-      <c r="I34" s="166" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="35" spans="2:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="B35" s="165"/>
-      <c r="C35" s="174"/>
-      <c r="D35" s="174"/>
-      <c r="E35" s="176"/>
+      <c r="I34" s="161" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B35" s="169"/>
+      <c r="C35" s="158"/>
+      <c r="D35" s="158"/>
+      <c r="E35" s="155"/>
       <c r="F35" s="16" t="s">
         <v>191</v>
       </c>
@@ -3250,13 +3333,13 @@
       <c r="H35" s="97" t="s">
         <v>192</v>
       </c>
-      <c r="I35" s="170"/>
-    </row>
-    <row r="36" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="181"/>
-      <c r="C36" s="184"/>
-      <c r="D36" s="184"/>
-      <c r="E36" s="192"/>
+      <c r="I35" s="160"/>
+    </row>
+    <row r="36" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="191"/>
+      <c r="C36" s="166"/>
+      <c r="D36" s="166"/>
+      <c r="E36" s="198"/>
       <c r="F36" s="43" t="s">
         <v>130</v>
       </c>
@@ -3264,16 +3347,16 @@
         <v>45989</v>
       </c>
       <c r="H36" s="101"/>
-      <c r="I36" s="167"/>
-    </row>
-    <row r="37" spans="2:12" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="152">
+      <c r="I36" s="151"/>
+    </row>
+    <row r="37" spans="2:12" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="188">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C37" s="154" t="s">
+      <c r="C37" s="194" t="s">
         <v>30</v>
       </c>
-      <c r="D37" s="154"/>
+      <c r="D37" s="194"/>
       <c r="E37" s="30" t="s">
         <v>95</v>
       </c>
@@ -3290,11 +3373,11 @@
         <v>131</v>
       </c>
     </row>
-    <row r="38" spans="2:12" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="165"/>
-      <c r="C38" s="174"/>
-      <c r="D38" s="174"/>
-      <c r="E38" s="176" t="s">
+    <row r="38" spans="2:12" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="169"/>
+      <c r="C38" s="158"/>
+      <c r="D38" s="158"/>
+      <c r="E38" s="155" t="s">
         <v>96</v>
       </c>
       <c r="F38" s="6" t="s">
@@ -3306,15 +3389,15 @@
       <c r="H38" s="97" t="s">
         <v>129</v>
       </c>
-      <c r="I38" s="168" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="39" spans="2:12" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="153"/>
-      <c r="C39" s="155"/>
-      <c r="D39" s="155"/>
-      <c r="E39" s="177"/>
+      <c r="I38" s="150" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="170"/>
+      <c r="C39" s="159"/>
+      <c r="D39" s="159"/>
+      <c r="E39" s="156"/>
       <c r="F39" s="31" t="s">
         <v>130</v>
       </c>
@@ -3322,16 +3405,16 @@
         <v>45981</v>
       </c>
       <c r="H39" s="94"/>
-      <c r="I39" s="167"/>
-    </row>
-    <row r="40" spans="2:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="B40" s="180">
+      <c r="I39" s="151"/>
+    </row>
+    <row r="40" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B40" s="168">
         <v>2.4</v>
       </c>
-      <c r="C40" s="215" t="s">
+      <c r="C40" s="146" t="s">
         <v>23</v>
       </c>
-      <c r="D40" s="191"/>
+      <c r="D40" s="157"/>
       <c r="E40" s="22" t="s">
         <v>97</v>
       </c>
@@ -3342,14 +3425,14 @@
         <v>45992</v>
       </c>
       <c r="H40" s="96"/>
-      <c r="I40" s="168" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="41" spans="2:12" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="181"/>
-      <c r="C41" s="216"/>
-      <c r="D41" s="184"/>
+      <c r="I40" s="150" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="191"/>
+      <c r="C41" s="190"/>
+      <c r="D41" s="166"/>
       <c r="E41" s="20" t="s">
         <v>98</v>
       </c>
@@ -3360,9 +3443,9 @@
         <v>45992</v>
       </c>
       <c r="H41" s="103"/>
-      <c r="I41" s="169"/>
-    </row>
-    <row r="42" spans="2:12" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I41" s="163"/>
+    </row>
+    <row r="42" spans="2:12" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="32">
         <v>2.5</v>
       </c>
@@ -3384,7 +3467,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="43" spans="2:12" ht="92.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:12" ht="92.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B43" s="32">
         <v>2.6</v>
       </c>
@@ -3406,20 +3489,20 @@
         <v>131</v>
       </c>
     </row>
-    <row r="44" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="144" t="s">
+    <row r="44" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B44" s="211" t="s">
         <v>60</v>
       </c>
-      <c r="C44" s="145"/>
-      <c r="D44" s="145"/>
-      <c r="E44" s="145"/>
-      <c r="F44" s="145"/>
-      <c r="G44" s="145"/>
-      <c r="H44" s="146"/>
+      <c r="C44" s="212"/>
+      <c r="D44" s="212"/>
+      <c r="E44" s="212"/>
+      <c r="F44" s="212"/>
+      <c r="G44" s="212"/>
+      <c r="H44" s="213"/>
       <c r="I44" s="58"/>
       <c r="L44" s="1"/>
     </row>
-    <row r="45" spans="2:12" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:12" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B45" s="32">
         <v>3.1</v>
       </c>
@@ -3441,7 +3524,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="46" spans="2:12" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:12" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B46" s="32">
         <v>3.2</v>
       </c>
@@ -3452,7 +3535,7 @@
       <c r="E46" s="48" t="s">
         <v>102</v>
       </c>
-      <c r="F46" s="225" t="s">
+      <c r="F46" s="242" t="s">
         <v>185</v>
       </c>
       <c r="G46" s="51">
@@ -3463,7 +3546,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="2:12" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:12" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="32">
         <v>3.3</v>
       </c>
@@ -3474,7 +3557,7 @@
       <c r="E47" s="47" t="s">
         <v>103</v>
       </c>
-      <c r="F47" s="226"/>
+      <c r="F47" s="243"/>
       <c r="G47" s="50">
         <v>45989</v>
       </c>
@@ -3483,7 +3566,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="48" spans="2:12" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:12" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B48" s="32">
         <v>3.4</v>
       </c>
@@ -3505,738 +3588,738 @@
         <v>131</v>
       </c>
     </row>
-    <row r="49" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="147" t="s">
+    <row r="49" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B49" s="235">
+        <v>3.5</v>
+      </c>
+      <c r="C49" s="236" t="s">
+        <v>229</v>
+      </c>
+      <c r="D49" s="237"/>
+      <c r="E49" s="65" t="s">
+        <v>231</v>
+      </c>
+      <c r="F49" s="49" t="s">
+        <v>130</v>
+      </c>
+      <c r="G49" s="66">
+        <v>46007</v>
+      </c>
+      <c r="H49" s="95"/>
+      <c r="I49" s="200" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="50" spans="2:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B50" s="203"/>
+      <c r="C50" s="205"/>
+      <c r="D50" s="207"/>
+      <c r="E50" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="G50" s="11">
+        <v>46007</v>
+      </c>
+      <c r="H50" s="241"/>
+      <c r="I50" s="201"/>
+    </row>
+    <row r="51" spans="2:12" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B51" s="204"/>
+      <c r="C51" s="206"/>
+      <c r="D51" s="208"/>
+      <c r="E51" s="68" t="s">
+        <v>232</v>
+      </c>
+      <c r="F51" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="G51" s="62">
+        <v>46007</v>
+      </c>
+      <c r="H51" s="105"/>
+      <c r="I51" s="202"/>
+    </row>
+    <row r="52" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B52" s="214" t="s">
         <v>68</v>
       </c>
-      <c r="C49" s="148"/>
-      <c r="D49" s="148"/>
-      <c r="E49" s="148"/>
-      <c r="F49" s="148"/>
-      <c r="G49" s="148"/>
-      <c r="H49" s="149"/>
-      <c r="I49" s="58"/>
-    </row>
-    <row r="50" spans="2:12" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="32">
+      <c r="C52" s="215"/>
+      <c r="D52" s="215"/>
+      <c r="E52" s="215"/>
+      <c r="F52" s="215"/>
+      <c r="G52" s="215"/>
+      <c r="H52" s="216"/>
+      <c r="I52" s="58"/>
+    </row>
+    <row r="53" spans="2:12" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B53" s="32">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C50" s="33" t="s">
+      <c r="C53" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="D50" s="33"/>
-      <c r="E50" s="34" t="s">
+      <c r="D53" s="33"/>
+      <c r="E53" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="F50" s="46" t="s">
-        <v>130</v>
-      </c>
-      <c r="G50" s="36">
+      <c r="F53" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="G53" s="36">
         <v>45965</v>
       </c>
-      <c r="H50" s="92"/>
-      <c r="I50" s="112" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="51" spans="2:12" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="32">
+      <c r="H53" s="92"/>
+      <c r="I53" s="112" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="54" spans="2:12" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B54" s="32">
         <v>4.2</v>
       </c>
-      <c r="C51" s="52" t="s">
+      <c r="C54" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="D51" s="52"/>
-      <c r="E51" s="34" t="s">
+      <c r="D54" s="52"/>
+      <c r="E54" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="F51" s="46" t="s">
-        <v>130</v>
-      </c>
-      <c r="G51" s="36">
+      <c r="F54" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="G54" s="36">
         <v>45965</v>
       </c>
-      <c r="H51" s="92"/>
-      <c r="I51" s="112" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="52" spans="2:12" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="63">
+      <c r="H54" s="92"/>
+      <c r="I54" s="112" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="55" spans="2:12" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B55" s="63">
         <v>4.3</v>
       </c>
-      <c r="C52" s="64" t="s">
+      <c r="C55" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="D52" s="64"/>
-      <c r="E52" s="65" t="s">
+      <c r="D55" s="64"/>
+      <c r="E55" s="65" t="s">
         <v>107</v>
       </c>
-      <c r="F52" s="49" t="s">
-        <v>130</v>
-      </c>
-      <c r="G52" s="66">
+      <c r="F55" s="49" t="s">
+        <v>130</v>
+      </c>
+      <c r="G55" s="66">
         <v>45988</v>
       </c>
-      <c r="H52" s="104"/>
-      <c r="I52" s="113" t="s">
-        <v>131</v>
-      </c>
-      <c r="L52"/>
-    </row>
-    <row r="53" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="150" t="s">
+      <c r="H55" s="104"/>
+      <c r="I55" s="113" t="s">
+        <v>131</v>
+      </c>
+      <c r="L55"/>
+    </row>
+    <row r="56" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B56" s="217" t="s">
         <v>67</v>
       </c>
-      <c r="C53" s="151"/>
-      <c r="D53" s="151"/>
-      <c r="E53" s="151"/>
-      <c r="F53" s="151"/>
-      <c r="G53" s="151"/>
-      <c r="H53" s="151"/>
-      <c r="I53" s="58"/>
-      <c r="L53" s="1"/>
-    </row>
-    <row r="54" spans="2:12" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="59">
+      <c r="C56" s="218"/>
+      <c r="D56" s="218"/>
+      <c r="E56" s="218"/>
+      <c r="F56" s="218"/>
+      <c r="G56" s="218"/>
+      <c r="H56" s="218"/>
+      <c r="I56" s="58"/>
+      <c r="L56" s="1"/>
+    </row>
+    <row r="57" spans="2:12" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B57" s="59">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C54" s="67" t="s">
+      <c r="C57" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="D54" s="67"/>
-      <c r="E54" s="68" t="s">
+      <c r="D57" s="67"/>
+      <c r="E57" s="68" t="s">
         <v>108</v>
       </c>
-      <c r="F54" s="53" t="s">
-        <v>130</v>
-      </c>
-      <c r="G54" s="62">
+      <c r="F57" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="G57" s="62">
         <v>45995</v>
       </c>
-      <c r="H54" s="105"/>
-      <c r="I54" s="114" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="55" spans="2:12" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="18">
+      <c r="H57" s="105"/>
+      <c r="I57" s="114" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="58" spans="2:12" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B58" s="18">
         <v>5.2</v>
       </c>
-      <c r="C55" s="54" t="s">
+      <c r="C58" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="D55" s="54"/>
-      <c r="E55" s="55" t="s">
+      <c r="D58" s="54"/>
+      <c r="E58" s="55" t="s">
         <v>110</v>
       </c>
-      <c r="F55" s="56" t="s">
-        <v>130</v>
-      </c>
-      <c r="G55" s="57">
+      <c r="F58" s="56" t="s">
+        <v>130</v>
+      </c>
+      <c r="G58" s="57">
         <v>45965</v>
       </c>
-      <c r="H55" s="106"/>
-      <c r="I55" s="115" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="56" spans="2:12" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="32">
+      <c r="H58" s="106"/>
+      <c r="I58" s="115" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="59" spans="2:12" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B59" s="32">
         <v>5.3</v>
       </c>
-      <c r="C56" s="52" t="s">
+      <c r="C59" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="D56" s="52"/>
-      <c r="E56" s="35" t="s">
+      <c r="D59" s="52"/>
+      <c r="E59" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="F56" s="46" t="s">
-        <v>130</v>
-      </c>
-      <c r="G56" s="36">
+      <c r="F59" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="G59" s="36">
         <v>45965</v>
       </c>
-      <c r="H56" s="92"/>
-      <c r="I56" s="112" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="57" spans="2:12" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="18">
+      <c r="H59" s="92"/>
+      <c r="I59" s="112" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="60" spans="2:12" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B60" s="18">
         <v>5.4</v>
       </c>
-      <c r="C57" s="54" t="s">
+      <c r="C60" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="D57" s="54"/>
-      <c r="E57" s="21" t="s">
+      <c r="D60" s="54"/>
+      <c r="E60" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="F57" s="56" t="s">
-        <v>130</v>
-      </c>
-      <c r="G57" s="57">
+      <c r="F60" s="56" t="s">
+        <v>130</v>
+      </c>
+      <c r="G60" s="57">
         <v>45995</v>
       </c>
-      <c r="H57" s="106"/>
-      <c r="I57" s="115" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="58" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="171" t="s">
+      <c r="H60" s="106"/>
+      <c r="I60" s="115" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="61" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B61" s="138" t="s">
         <v>66</v>
       </c>
-      <c r="C58" s="172"/>
-      <c r="D58" s="172"/>
-      <c r="E58" s="172"/>
-      <c r="F58" s="172"/>
-      <c r="G58" s="172"/>
-      <c r="H58" s="172"/>
-      <c r="I58" s="58"/>
-    </row>
-    <row r="59" spans="2:12" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="59">
+      <c r="C61" s="139"/>
+      <c r="D61" s="139"/>
+      <c r="E61" s="139"/>
+      <c r="F61" s="139"/>
+      <c r="G61" s="139"/>
+      <c r="H61" s="139"/>
+      <c r="I61" s="58"/>
+    </row>
+    <row r="62" spans="2:12" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B62" s="59">
         <v>6.1</v>
       </c>
-      <c r="C59" s="60" t="s">
+      <c r="C62" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="D59" s="60"/>
-      <c r="E59" s="61" t="s">
+      <c r="D62" s="60"/>
+      <c r="E62" s="61" t="s">
         <v>152</v>
       </c>
-      <c r="F59" s="53" t="s">
-        <v>130</v>
-      </c>
-      <c r="G59" s="62">
+      <c r="F62" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="G62" s="62">
         <v>45985</v>
       </c>
-      <c r="H59" s="105"/>
-      <c r="I59" s="114" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="60" spans="2:12" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="152">
+      <c r="H62" s="105"/>
+      <c r="I62" s="114" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="63" spans="2:12" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B63" s="188">
         <v>6.2</v>
       </c>
-      <c r="C60" s="154" t="s">
+      <c r="C63" s="194" t="s">
         <v>16</v>
       </c>
-      <c r="D60" s="154"/>
-      <c r="E60" s="69" t="s">
+      <c r="D63" s="194"/>
+      <c r="E63" s="69" t="s">
         <v>153</v>
       </c>
-      <c r="F60" s="70" t="s">
-        <v>130</v>
-      </c>
-      <c r="G60" s="38">
+      <c r="F63" s="70" t="s">
+        <v>130</v>
+      </c>
+      <c r="G63" s="38">
         <v>45985</v>
       </c>
-      <c r="H60" s="93"/>
-      <c r="I60" s="113" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="61" spans="2:12" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="165"/>
-      <c r="C61" s="174"/>
-      <c r="D61" s="174"/>
-      <c r="E61" s="176" t="s">
+      <c r="H63" s="93"/>
+      <c r="I63" s="113" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="64" spans="2:12" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B64" s="169"/>
+      <c r="C64" s="158"/>
+      <c r="D64" s="158"/>
+      <c r="E64" s="155" t="s">
         <v>154</v>
       </c>
-      <c r="F61" s="16" t="s">
+      <c r="F64" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="G61" s="11">
+      <c r="G64" s="11">
         <v>45985</v>
       </c>
-      <c r="H61" s="100" t="s">
+      <c r="H64" s="100" t="s">
         <v>162</v>
       </c>
-      <c r="I61" s="166" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="62" spans="2:12" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="153"/>
-      <c r="C62" s="155"/>
-      <c r="D62" s="155"/>
-      <c r="E62" s="177"/>
-      <c r="F62" s="41" t="s">
-        <v>130</v>
-      </c>
-      <c r="G62" s="40">
+      <c r="I64" s="161" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="65" spans="2:9" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B65" s="170"/>
+      <c r="C65" s="159"/>
+      <c r="D65" s="159"/>
+      <c r="E65" s="156"/>
+      <c r="F65" s="41" t="s">
+        <v>130</v>
+      </c>
+      <c r="G65" s="40">
         <v>45985</v>
       </c>
-      <c r="H62" s="99"/>
-      <c r="I62" s="167"/>
-    </row>
-    <row r="63" spans="2:12" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="18">
+      <c r="H65" s="99"/>
+      <c r="I65" s="151"/>
+    </row>
+    <row r="66" spans="2:9" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B66" s="18">
         <v>6.3</v>
       </c>
-      <c r="C63" s="54" t="s">
+      <c r="C66" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="D63" s="54"/>
-      <c r="E63" s="21" t="s">
+      <c r="D66" s="54"/>
+      <c r="E66" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="F63" s="56" t="s">
-        <v>130</v>
-      </c>
-      <c r="G63" s="57">
+      <c r="F66" s="56" t="s">
+        <v>130</v>
+      </c>
+      <c r="G66" s="57">
         <v>45965</v>
       </c>
-      <c r="H63" s="106"/>
-      <c r="I63" s="115" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="64" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="163" t="s">
+      <c r="H66" s="106"/>
+      <c r="I66" s="115" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="67" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B67" s="224" t="s">
         <v>65</v>
       </c>
-      <c r="C64" s="164"/>
-      <c r="D64" s="164"/>
-      <c r="E64" s="164"/>
-      <c r="F64" s="164"/>
-      <c r="G64" s="164"/>
-      <c r="H64" s="164"/>
-      <c r="I64" s="58"/>
-    </row>
-    <row r="65" spans="2:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="152">
+      <c r="C67" s="225"/>
+      <c r="D67" s="225"/>
+      <c r="E67" s="225"/>
+      <c r="F67" s="225"/>
+      <c r="G67" s="225"/>
+      <c r="H67" s="225"/>
+      <c r="I67" s="58"/>
+    </row>
+    <row r="68" spans="2:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B68" s="188">
         <v>7.1</v>
       </c>
-      <c r="C65" s="154" t="s">
+      <c r="C68" s="194" t="s">
         <v>163</v>
       </c>
-      <c r="D65" s="154" t="s">
+      <c r="D68" s="194" t="s">
         <v>164</v>
       </c>
-      <c r="E65" s="175" t="s">
+      <c r="E68" s="162" t="s">
         <v>170</v>
       </c>
-      <c r="F65" s="30" t="s">
+      <c r="F68" s="30" t="s">
         <v>172</v>
       </c>
-      <c r="G65" s="38">
+      <c r="G68" s="38">
         <v>45985</v>
       </c>
-      <c r="H65" s="223" t="s">
+      <c r="H68" s="153" t="s">
         <v>174</v>
       </c>
-      <c r="I65" s="166" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="66" spans="2:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="165"/>
-      <c r="C66" s="174"/>
-      <c r="D66" s="174"/>
-      <c r="E66" s="176"/>
-      <c r="F66" s="6" t="s">
+      <c r="I68" s="161" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="69" spans="2:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="169"/>
+      <c r="C69" s="158"/>
+      <c r="D69" s="158"/>
+      <c r="E69" s="155"/>
+      <c r="F69" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="G66" s="11">
+      <c r="G69" s="11">
         <v>45985</v>
       </c>
-      <c r="H66" s="224"/>
-      <c r="I66" s="170"/>
-    </row>
-    <row r="67" spans="2:9" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="165"/>
-      <c r="C67" s="174"/>
-      <c r="D67" s="174"/>
-      <c r="E67" s="176"/>
-      <c r="F67" s="6" t="s">
+      <c r="H69" s="154"/>
+      <c r="I69" s="160"/>
+    </row>
+    <row r="70" spans="2:9" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B70" s="169"/>
+      <c r="C70" s="158"/>
+      <c r="D70" s="158"/>
+      <c r="E70" s="155"/>
+      <c r="F70" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="G67" s="11">
+      <c r="G70" s="11">
         <v>45985</v>
       </c>
-      <c r="H67" s="224"/>
-      <c r="I67" s="170"/>
-    </row>
-    <row r="68" spans="2:9" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="153"/>
-      <c r="C68" s="155"/>
-      <c r="D68" s="155"/>
-      <c r="E68" s="177"/>
-      <c r="F68" s="41" t="s">
-        <v>130</v>
-      </c>
-      <c r="G68" s="40">
+      <c r="H70" s="154"/>
+      <c r="I70" s="160"/>
+    </row>
+    <row r="71" spans="2:9" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B71" s="170"/>
+      <c r="C71" s="159"/>
+      <c r="D71" s="159"/>
+      <c r="E71" s="156"/>
+      <c r="F71" s="41" t="s">
+        <v>130</v>
+      </c>
+      <c r="G71" s="40">
         <v>45995</v>
       </c>
-      <c r="H68" s="94"/>
-      <c r="I68" s="167"/>
-    </row>
-    <row r="69" spans="2:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="180">
+      <c r="H71" s="94"/>
+      <c r="I71" s="151"/>
+    </row>
+    <row r="72" spans="2:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B72" s="168">
         <v>7.2</v>
       </c>
-      <c r="C69" s="191" t="s">
+      <c r="C72" s="157" t="s">
         <v>17</v>
       </c>
-      <c r="D69" s="191"/>
-      <c r="E69" s="28" t="s">
+      <c r="D72" s="157"/>
+      <c r="E72" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="F69" s="42" t="s">
-        <v>130</v>
-      </c>
-      <c r="G69" s="29">
+      <c r="F72" s="42" t="s">
+        <v>130</v>
+      </c>
+      <c r="G72" s="29">
         <v>45987</v>
       </c>
-      <c r="H69" s="96"/>
-      <c r="I69" s="115" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="70" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="165"/>
-      <c r="C70" s="174"/>
-      <c r="D70" s="174"/>
-      <c r="E70" s="176" t="s">
+      <c r="H72" s="96"/>
+      <c r="I72" s="115" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="73" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B73" s="169"/>
+      <c r="C73" s="158"/>
+      <c r="D73" s="158"/>
+      <c r="E73" s="155" t="s">
         <v>177</v>
       </c>
-      <c r="F70" s="16" t="s">
+      <c r="F73" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="G70" s="11">
+      <c r="G73" s="11">
         <v>45980</v>
       </c>
-      <c r="H70" s="100" t="s">
+      <c r="H73" s="100" t="s">
         <v>175</v>
       </c>
-      <c r="I70" s="166" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="71" spans="2:9" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="165"/>
-      <c r="C71" s="174"/>
-      <c r="D71" s="174"/>
-      <c r="E71" s="176"/>
-      <c r="F71" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="G71" s="11">
+      <c r="I73" s="161" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="74" spans="2:9" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="169"/>
+      <c r="C74" s="158"/>
+      <c r="D74" s="158"/>
+      <c r="E74" s="155"/>
+      <c r="F74" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="G74" s="11">
         <v>45980</v>
       </c>
-      <c r="H71" s="100"/>
-      <c r="I71" s="167"/>
-    </row>
-    <row r="72" spans="2:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="165"/>
-      <c r="C72" s="174"/>
-      <c r="D72" s="174"/>
-      <c r="E72" s="176" t="s">
+      <c r="H74" s="100"/>
+      <c r="I74" s="151"/>
+    </row>
+    <row r="75" spans="2:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="169"/>
+      <c r="C75" s="158"/>
+      <c r="D75" s="158"/>
+      <c r="E75" s="155" t="s">
         <v>178</v>
       </c>
-      <c r="F72" s="6" t="s">
+      <c r="F75" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="G72" s="11"/>
-      <c r="H72" s="100" t="s">
+      <c r="G75" s="11"/>
+      <c r="H75" s="100" t="s">
         <v>195</v>
       </c>
-      <c r="I72" s="168" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="73" spans="2:9" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="181"/>
-      <c r="C73" s="184"/>
-      <c r="D73" s="184"/>
-      <c r="E73" s="192"/>
-      <c r="F73" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="G73" s="44">
+      <c r="I75" s="150" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="76" spans="2:9" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B76" s="191"/>
+      <c r="C76" s="166"/>
+      <c r="D76" s="166"/>
+      <c r="E76" s="198"/>
+      <c r="F76" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="G76" s="44">
         <v>45992</v>
       </c>
-      <c r="H73" s="101"/>
-      <c r="I73" s="169"/>
-    </row>
-    <row r="74" spans="2:9" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="152">
+      <c r="H76" s="101"/>
+      <c r="I76" s="163"/>
+    </row>
+    <row r="77" spans="2:9" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B77" s="188">
         <v>7.3</v>
       </c>
-      <c r="C74" s="154" t="s">
+      <c r="C77" s="194" t="s">
         <v>18</v>
       </c>
-      <c r="D74" s="185" t="s">
+      <c r="D77" s="148" t="s">
         <v>165</v>
       </c>
-      <c r="E74" s="178" t="s">
+      <c r="E77" s="199" t="s">
         <v>113</v>
       </c>
-      <c r="F74" s="71" t="s">
+      <c r="F77" s="71" t="s">
         <v>167</v>
       </c>
-      <c r="G74" s="38">
+      <c r="G77" s="38">
         <v>45932</v>
       </c>
-      <c r="H74" s="107" t="s">
+      <c r="H77" s="107" t="s">
         <v>166</v>
       </c>
-      <c r="I74" s="166" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="75" spans="2:9" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="165"/>
-      <c r="C75" s="174"/>
-      <c r="D75" s="186"/>
-      <c r="E75" s="179"/>
-      <c r="F75" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="G75" s="11">
+      <c r="I77" s="161" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="78" spans="2:9" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B78" s="169"/>
+      <c r="C78" s="158"/>
+      <c r="D78" s="189"/>
+      <c r="E78" s="152"/>
+      <c r="F78" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="G78" s="11">
         <v>45933</v>
       </c>
-      <c r="H75" s="100"/>
-      <c r="I75" s="169"/>
-    </row>
-    <row r="76" spans="2:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="165"/>
-      <c r="C76" s="174"/>
-      <c r="D76" s="186"/>
-      <c r="E76" s="179" t="s">
+      <c r="H78" s="100"/>
+      <c r="I78" s="163"/>
+    </row>
+    <row r="79" spans="2:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="169"/>
+      <c r="C79" s="158"/>
+      <c r="D79" s="189"/>
+      <c r="E79" s="152" t="s">
         <v>114</v>
       </c>
-      <c r="F76" s="6" t="s">
+      <c r="F79" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="G76" s="11">
+      <c r="G79" s="11">
         <v>45943</v>
       </c>
-      <c r="H76" s="100" t="s">
+      <c r="H79" s="100" t="s">
         <v>169</v>
       </c>
-      <c r="I76" s="166" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="77" spans="2:9" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="165"/>
-      <c r="C77" s="174"/>
-      <c r="D77" s="186"/>
-      <c r="E77" s="179"/>
-      <c r="F77" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="G77" s="11">
+      <c r="I79" s="161" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="80" spans="2:9" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B80" s="169"/>
+      <c r="C80" s="158"/>
+      <c r="D80" s="189"/>
+      <c r="E80" s="152"/>
+      <c r="F80" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="G80" s="11">
         <v>45967</v>
       </c>
-      <c r="H77" s="74"/>
-      <c r="I77" s="167"/>
-    </row>
-    <row r="78" spans="2:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="153"/>
-      <c r="C78" s="155"/>
-      <c r="D78" s="187"/>
-      <c r="E78" s="31" t="s">
+      <c r="H80" s="74"/>
+      <c r="I80" s="151"/>
+    </row>
+    <row r="81" spans="2:9" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B81" s="170"/>
+      <c r="C81" s="159"/>
+      <c r="D81" s="149"/>
+      <c r="E81" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="F78" s="72" t="s">
-        <v>130</v>
-      </c>
-      <c r="G78" s="40">
+      <c r="F81" s="72" t="s">
+        <v>130</v>
+      </c>
+      <c r="G81" s="40">
         <v>45967</v>
       </c>
-      <c r="H78" s="94"/>
-      <c r="I78" s="114" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="79" spans="2:9" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="152">
+      <c r="H81" s="94"/>
+      <c r="I81" s="114" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="82" spans="2:9" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B82" s="188">
         <v>7.4</v>
       </c>
-      <c r="C79" s="154" t="s">
+      <c r="C82" s="194" t="s">
         <v>19</v>
       </c>
-      <c r="D79" s="154"/>
-      <c r="E79" s="175" t="s">
+      <c r="D82" s="194"/>
+      <c r="E82" s="162" t="s">
         <v>198</v>
       </c>
-      <c r="F79" s="71" t="s">
+      <c r="F82" s="71" t="s">
         <v>135</v>
       </c>
-      <c r="G79" s="38">
+      <c r="G82" s="38">
         <v>45985</v>
       </c>
-      <c r="H79" s="102" t="s">
+      <c r="H82" s="102" t="s">
         <v>158</v>
       </c>
-      <c r="I79" s="166" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="80" spans="2:9" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B80" s="165"/>
-      <c r="C80" s="174"/>
-      <c r="D80" s="174"/>
-      <c r="E80" s="176"/>
-      <c r="F80" s="6" t="s">
+      <c r="I82" s="161" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="83" spans="2:9" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B83" s="169"/>
+      <c r="C83" s="158"/>
+      <c r="D83" s="158"/>
+      <c r="E83" s="155"/>
+      <c r="F83" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="G80" s="11">
+      <c r="G83" s="11">
         <v>45985</v>
       </c>
-      <c r="H80" s="108" t="s">
+      <c r="H83" s="108" t="s">
         <v>161</v>
       </c>
-      <c r="I80" s="170"/>
-    </row>
-    <row r="81" spans="2:9" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="165"/>
-      <c r="C81" s="174"/>
-      <c r="D81" s="174"/>
-      <c r="E81" s="176"/>
-      <c r="F81" s="6" t="s">
+      <c r="I83" s="160"/>
+    </row>
+    <row r="84" spans="2:9" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B84" s="169"/>
+      <c r="C84" s="158"/>
+      <c r="D84" s="158"/>
+      <c r="E84" s="155"/>
+      <c r="F84" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="G81" s="11">
+      <c r="G84" s="11">
         <v>45995</v>
       </c>
-      <c r="H81" s="108" t="s">
+      <c r="H84" s="108" t="s">
         <v>200</v>
       </c>
-      <c r="I81" s="170"/>
-    </row>
-    <row r="82" spans="2:9" ht="57.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="165"/>
-      <c r="C82" s="174"/>
-      <c r="D82" s="174"/>
-      <c r="E82" s="176"/>
-      <c r="F82" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="G82" s="11">
+      <c r="I84" s="160"/>
+    </row>
+    <row r="85" spans="2:9" ht="57.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B85" s="169"/>
+      <c r="C85" s="158"/>
+      <c r="D85" s="158"/>
+      <c r="E85" s="155"/>
+      <c r="F85" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="G85" s="11">
         <v>45995</v>
       </c>
-      <c r="H82" s="108"/>
-      <c r="I82" s="167"/>
-    </row>
-    <row r="83" spans="2:9" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="165"/>
-      <c r="C83" s="174"/>
-      <c r="D83" s="174"/>
-      <c r="E83" s="176" t="s">
+      <c r="H85" s="108"/>
+      <c r="I85" s="151"/>
+    </row>
+    <row r="86" spans="2:9" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B86" s="169"/>
+      <c r="C86" s="158"/>
+      <c r="D86" s="158"/>
+      <c r="E86" s="155" t="s">
         <v>157</v>
       </c>
-      <c r="F83" s="6" t="s">
+      <c r="F86" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="G83" s="11">
+      <c r="G86" s="11">
         <v>45986</v>
       </c>
-      <c r="H83" s="97" t="s">
+      <c r="H86" s="97" t="s">
         <v>156</v>
       </c>
-      <c r="I83" s="168" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="84" spans="2:9" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B84" s="153"/>
-      <c r="C84" s="155"/>
-      <c r="D84" s="155"/>
-      <c r="E84" s="177"/>
-      <c r="F84" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="G84" s="40">
+      <c r="I86" s="150" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="87" spans="2:9" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B87" s="170"/>
+      <c r="C87" s="159"/>
+      <c r="D87" s="159"/>
+      <c r="E87" s="156"/>
+      <c r="F87" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="G87" s="40">
         <v>45987</v>
       </c>
-      <c r="H84" s="94"/>
-      <c r="I84" s="167"/>
-    </row>
-    <row r="85" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B85" s="144" t="s">
+      <c r="H87" s="94"/>
+      <c r="I87" s="151"/>
+    </row>
+    <row r="88" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B88" s="211" t="s">
         <v>64</v>
       </c>
-      <c r="C85" s="145"/>
-      <c r="D85" s="145"/>
-      <c r="E85" s="145"/>
-      <c r="F85" s="145"/>
-      <c r="G85" s="145"/>
-      <c r="H85" s="146"/>
-      <c r="I85" s="58"/>
-    </row>
-    <row r="86" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="152">
+      <c r="C88" s="212"/>
+      <c r="D88" s="212"/>
+      <c r="E88" s="212"/>
+      <c r="F88" s="212"/>
+      <c r="G88" s="212"/>
+      <c r="H88" s="213"/>
+      <c r="I88" s="58"/>
+    </row>
+    <row r="89" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B89" s="188">
         <v>8.1</v>
       </c>
-      <c r="C86" s="154" t="s">
+      <c r="C89" s="194" t="s">
         <v>34</v>
       </c>
-      <c r="D86" s="156"/>
-      <c r="E86" s="30" t="s">
+      <c r="D89" s="192"/>
+      <c r="E89" s="30" t="s">
         <v>179</v>
-      </c>
-      <c r="F86" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="G86" s="38">
-        <v>45980</v>
-      </c>
-      <c r="H86" s="93"/>
-      <c r="I86" s="166" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="87" spans="2:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="165"/>
-      <c r="C87" s="174"/>
-      <c r="D87" s="182"/>
-      <c r="E87" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="F87" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="G87" s="11">
-        <v>45980</v>
-      </c>
-      <c r="H87" s="74"/>
-      <c r="I87" s="199"/>
-    </row>
-    <row r="88" spans="2:9" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B88" s="153"/>
-      <c r="C88" s="155"/>
-      <c r="D88" s="157"/>
-      <c r="E88" s="31" t="s">
-        <v>181</v>
-      </c>
-      <c r="F88" s="31" t="s">
-        <v>182</v>
-      </c>
-      <c r="G88" s="40">
-        <v>45980</v>
-      </c>
-      <c r="H88" s="94"/>
-      <c r="I88" s="200"/>
-    </row>
-    <row r="89" spans="2:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="B89" s="152">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="C89" s="154" t="s">
-        <v>33</v>
-      </c>
-      <c r="D89" s="156"/>
-      <c r="E89" s="30" t="s">
-        <v>116</v>
       </c>
       <c r="F89" s="30" t="s">
         <v>130</v>
@@ -4245,603 +4328,799 @@
         <v>45980</v>
       </c>
       <c r="H89" s="93"/>
-      <c r="I89" s="116" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="90" spans="2:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B90" s="153"/>
-      <c r="C90" s="155"/>
-      <c r="D90" s="157"/>
-      <c r="E90" s="31" t="s">
+      <c r="I89" s="161" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B90" s="169"/>
+      <c r="C90" s="158"/>
+      <c r="D90" s="172"/>
+      <c r="E90" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="G90" s="11">
+        <v>45980</v>
+      </c>
+      <c r="H90" s="74"/>
+      <c r="I90" s="164"/>
+    </row>
+    <row r="91" spans="2:9" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B91" s="170"/>
+      <c r="C91" s="159"/>
+      <c r="D91" s="173"/>
+      <c r="E91" s="31" t="s">
+        <v>181</v>
+      </c>
+      <c r="F91" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="G91" s="40">
+        <v>45980</v>
+      </c>
+      <c r="H91" s="94"/>
+      <c r="I91" s="165"/>
+    </row>
+    <row r="92" spans="2:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B92" s="188">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="C92" s="194" t="s">
+        <v>33</v>
+      </c>
+      <c r="D92" s="192"/>
+      <c r="E92" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="F92" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="G92" s="38">
+        <v>45980</v>
+      </c>
+      <c r="H92" s="93"/>
+      <c r="I92" s="116" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B93" s="170"/>
+      <c r="C93" s="159"/>
+      <c r="D93" s="173"/>
+      <c r="E93" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="F90" s="39" t="s">
-        <v>130</v>
-      </c>
-      <c r="G90" s="40">
+      <c r="F93" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="G93" s="40">
         <v>46009</v>
       </c>
-      <c r="H90" s="94"/>
-      <c r="I90" s="117" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="91" spans="2:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B91" s="32">
+      <c r="H93" s="94"/>
+      <c r="I93" s="117" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="94" spans="2:9" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B94" s="32">
         <v>8.3000000000000007</v>
       </c>
-      <c r="C91" s="52" t="s">
+      <c r="C94" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="D91" s="45"/>
-      <c r="E91" s="34" t="s">
+      <c r="D94" s="45"/>
+      <c r="E94" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="F91" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="G91" s="36">
+      <c r="F94" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="G94" s="36">
         <v>45980</v>
       </c>
-      <c r="H91" s="92"/>
-      <c r="I91" s="112" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="92" spans="2:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B92" s="18">
+      <c r="H94" s="92"/>
+      <c r="I94" s="112" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="95" spans="2:9" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B95" s="18">
         <v>8.4</v>
       </c>
-      <c r="C92" s="54" t="s">
+      <c r="C95" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="D92" s="27"/>
-      <c r="E92" s="21" t="s">
+      <c r="D95" s="27"/>
+      <c r="E95" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="F92" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="G92" s="57">
+      <c r="F95" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="G95" s="57">
         <v>45980</v>
       </c>
-      <c r="H92" s="106"/>
-      <c r="I92" s="117" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="93" spans="2:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="B93" s="152">
+      <c r="H95" s="106"/>
+      <c r="I95" s="117" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="96" spans="2:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B96" s="188">
         <v>8.5</v>
       </c>
-      <c r="C93" s="154" t="s">
+      <c r="C96" s="194" t="s">
         <v>36</v>
       </c>
-      <c r="D93" s="156"/>
-      <c r="E93" s="30" t="s">
+      <c r="D96" s="192"/>
+      <c r="E96" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="F93" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="G93" s="38">
+      <c r="F96" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="G96" s="38">
         <v>45980</v>
       </c>
-      <c r="H93" s="93"/>
-      <c r="I93" s="110" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="94" spans="2:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="B94" s="165"/>
-      <c r="C94" s="174"/>
-      <c r="D94" s="182"/>
-      <c r="E94" s="5" t="s">
+      <c r="H96" s="93"/>
+      <c r="I96" s="110" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="97" spans="2:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B97" s="169"/>
+      <c r="C97" s="158"/>
+      <c r="D97" s="172"/>
+      <c r="E97" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="F94" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="G94" s="11">
+      <c r="F97" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="G97" s="11">
         <v>45980</v>
       </c>
-      <c r="H94" s="74"/>
-      <c r="I94" s="111" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="95" spans="2:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="B95" s="165"/>
-      <c r="C95" s="174"/>
-      <c r="D95" s="182"/>
-      <c r="E95" s="176" t="s">
+      <c r="H97" s="74"/>
+      <c r="I97" s="111" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="98" spans="2:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B98" s="169"/>
+      <c r="C98" s="158"/>
+      <c r="D98" s="172"/>
+      <c r="E98" s="155" t="s">
         <v>122</v>
       </c>
-      <c r="F95" s="17" t="s">
+      <c r="F98" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="G95" s="11">
+      <c r="G98" s="11">
         <v>45980</v>
       </c>
-      <c r="H95" s="100" t="s">
+      <c r="H98" s="100" t="s">
         <v>184</v>
       </c>
-      <c r="I95" s="170" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="96" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B96" s="181"/>
-      <c r="C96" s="184"/>
-      <c r="D96" s="183"/>
-      <c r="E96" s="192"/>
-      <c r="F96" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="G96" s="44">
+      <c r="I98" s="160" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="99" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B99" s="191"/>
+      <c r="C99" s="166"/>
+      <c r="D99" s="193"/>
+      <c r="E99" s="198"/>
+      <c r="F99" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="G99" s="44">
         <v>45980</v>
       </c>
-      <c r="H96" s="103"/>
-      <c r="I96" s="169"/>
-    </row>
-    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B97" s="195" t="s">
+      <c r="H99" s="103"/>
+      <c r="I99" s="163"/>
+    </row>
+    <row r="100" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B100" s="228" t="s">
         <v>63</v>
       </c>
-      <c r="C97" s="196"/>
-      <c r="D97" s="196"/>
-      <c r="E97" s="196"/>
-      <c r="F97" s="196"/>
-      <c r="G97" s="196"/>
-      <c r="H97" s="196"/>
-      <c r="I97" s="73"/>
-    </row>
-    <row r="98" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B98" s="193" t="s">
+      <c r="C100" s="229"/>
+      <c r="D100" s="229"/>
+      <c r="E100" s="229"/>
+      <c r="F100" s="229"/>
+      <c r="G100" s="229"/>
+      <c r="H100" s="229"/>
+      <c r="I100" s="73"/>
+    </row>
+    <row r="101" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B101" s="226" t="s">
         <v>151</v>
       </c>
-      <c r="C98" s="194"/>
-      <c r="D98" s="194"/>
-      <c r="E98" s="194"/>
-      <c r="F98" s="194"/>
-      <c r="G98" s="194"/>
-      <c r="H98" s="77"/>
-      <c r="I98" s="118"/>
-    </row>
-    <row r="99" spans="2:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="B99" s="180">
+      <c r="C101" s="227"/>
+      <c r="D101" s="227"/>
+      <c r="E101" s="227"/>
+      <c r="F101" s="227"/>
+      <c r="G101" s="227"/>
+      <c r="H101" s="77"/>
+      <c r="I101" s="118"/>
+    </row>
+    <row r="102" spans="2:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B102" s="168">
         <v>9.1</v>
       </c>
-      <c r="C99" s="191" t="s">
+      <c r="C102" s="157" t="s">
         <v>37</v>
       </c>
-      <c r="D99" s="197"/>
-      <c r="E99" s="198" t="s">
+      <c r="D102" s="171"/>
+      <c r="E102" s="174" t="s">
         <v>124</v>
       </c>
-      <c r="F99" s="75" t="s">
+      <c r="F102" s="75" t="s">
         <v>136</v>
       </c>
-      <c r="G99" s="29">
+      <c r="G102" s="29">
         <v>45985</v>
       </c>
-      <c r="H99" s="96" t="s">
+      <c r="H102" s="96" t="s">
         <v>141</v>
       </c>
-      <c r="I99" s="168" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="100" spans="2:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="B100" s="165"/>
-      <c r="C100" s="174"/>
-      <c r="D100" s="182"/>
-      <c r="E100" s="176"/>
-      <c r="F100" s="8" t="s">
+      <c r="I102" s="150" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="103" spans="2:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B103" s="169"/>
+      <c r="C103" s="158"/>
+      <c r="D103" s="172"/>
+      <c r="E103" s="155"/>
+      <c r="F103" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="G100" s="11">
+      <c r="G103" s="11">
         <v>45985</v>
       </c>
-      <c r="H100" s="74"/>
-      <c r="I100" s="170"/>
-    </row>
-    <row r="101" spans="2:9" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B101" s="165"/>
-      <c r="C101" s="174"/>
-      <c r="D101" s="182"/>
-      <c r="E101" s="176" t="s">
+      <c r="H103" s="74"/>
+      <c r="I103" s="160"/>
+    </row>
+    <row r="104" spans="2:9" ht="81.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B104" s="169"/>
+      <c r="C104" s="158"/>
+      <c r="D104" s="172"/>
+      <c r="E104" s="155" t="s">
         <v>125</v>
       </c>
-      <c r="F101" s="6" t="s">
+      <c r="F104" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="G101" s="11">
+      <c r="G104" s="11">
         <v>45985</v>
       </c>
-      <c r="H101" s="97" t="s">
+      <c r="H104" s="97" t="s">
         <v>139</v>
       </c>
-      <c r="I101" s="170" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="102" spans="2:9" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B102" s="153"/>
-      <c r="C102" s="155"/>
-      <c r="D102" s="157"/>
-      <c r="E102" s="177"/>
-      <c r="F102" s="31" t="s">
+      <c r="I104" s="160" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="105" spans="2:9" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B105" s="170"/>
+      <c r="C105" s="159"/>
+      <c r="D105" s="173"/>
+      <c r="E105" s="156"/>
+      <c r="F105" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="G102" s="40">
+      <c r="G105" s="40">
         <v>45985</v>
       </c>
-      <c r="H102" s="98"/>
-      <c r="I102" s="167"/>
-    </row>
-    <row r="103" spans="2:9" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B103" s="18">
+      <c r="H105" s="98"/>
+      <c r="I105" s="151"/>
+    </row>
+    <row r="106" spans="2:9" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B106" s="18">
         <v>9.1999999999999993</v>
       </c>
-      <c r="C103" s="54" t="s">
+      <c r="C106" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="D103" s="27"/>
-      <c r="E103" s="21" t="s">
+      <c r="D106" s="27"/>
+      <c r="E106" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="F103" s="56" t="s">
-        <v>130</v>
-      </c>
-      <c r="G103" s="57">
+      <c r="F106" s="56" t="s">
+        <v>130</v>
+      </c>
+      <c r="G106" s="57">
         <v>45985</v>
       </c>
-      <c r="H103" s="106"/>
-      <c r="I103" s="115" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="104" spans="2:9" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B104" s="152">
+      <c r="H106" s="106"/>
+      <c r="I106" s="115" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="107" spans="2:9" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B107" s="188">
         <v>9.3000000000000007</v>
       </c>
-      <c r="C104" s="154" t="s">
+      <c r="C107" s="194" t="s">
         <v>39</v>
       </c>
-      <c r="D104" s="156"/>
-      <c r="E104" s="175" t="s">
+      <c r="D107" s="192"/>
+      <c r="E107" s="162" t="s">
         <v>142</v>
       </c>
-      <c r="F104" s="71" t="s">
+      <c r="F107" s="71" t="s">
         <v>143</v>
       </c>
-      <c r="G104" s="38">
+      <c r="G107" s="38">
         <v>45982</v>
       </c>
-      <c r="H104" s="102" t="s">
+      <c r="H107" s="102" t="s">
         <v>144</v>
       </c>
-      <c r="I104" s="166" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="105" spans="2:9" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B105" s="181"/>
-      <c r="C105" s="184"/>
-      <c r="D105" s="183"/>
-      <c r="E105" s="192"/>
-      <c r="F105" s="125" t="s">
+      <c r="I107" s="161" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="108" spans="2:9" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B108" s="191"/>
+      <c r="C108" s="166"/>
+      <c r="D108" s="193"/>
+      <c r="E108" s="198"/>
+      <c r="F108" s="125" t="s">
         <v>145</v>
       </c>
-      <c r="G105" s="44">
+      <c r="G108" s="44">
         <v>45982</v>
       </c>
-      <c r="H105" s="103"/>
-      <c r="I105" s="169"/>
-    </row>
-    <row r="106" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B106" s="152">
+      <c r="H108" s="103"/>
+      <c r="I108" s="163"/>
+    </row>
+    <row r="109" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B109" s="188">
         <v>9.4</v>
       </c>
-      <c r="C106" s="154" t="s">
+      <c r="C109" s="194" t="s">
         <v>40</v>
       </c>
-      <c r="D106" s="156"/>
-      <c r="E106" s="158" t="s">
+      <c r="D109" s="192"/>
+      <c r="E109" s="219" t="s">
         <v>127</v>
       </c>
-      <c r="F106" s="127" t="s">
+      <c r="F109" s="127" t="s">
         <v>146</v>
       </c>
-      <c r="G106" s="38">
+      <c r="G109" s="38">
         <v>45982</v>
       </c>
-      <c r="H106" s="161" t="s">
+      <c r="H109" s="222" t="s">
+        <v>216</v>
+      </c>
+      <c r="I109" s="200" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="110" spans="2:9" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B110" s="203"/>
+      <c r="C110" s="205"/>
+      <c r="D110" s="207"/>
+      <c r="E110" s="220"/>
+      <c r="F110" s="128" t="s">
         <v>217</v>
       </c>
-      <c r="I106" s="133" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="107" spans="2:9" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B107" s="136"/>
-      <c r="C107" s="138"/>
-      <c r="D107" s="140"/>
-      <c r="E107" s="159"/>
-      <c r="F107" s="128" t="s">
-        <v>218</v>
-      </c>
-      <c r="G107" s="57">
+      <c r="G110" s="57">
         <v>46030</v>
       </c>
-      <c r="H107" s="162"/>
-      <c r="I107" s="134"/>
-    </row>
-    <row r="108" spans="2:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B108" s="153"/>
-      <c r="C108" s="155"/>
-      <c r="D108" s="157"/>
-      <c r="E108" s="160"/>
-      <c r="F108" s="72" t="s">
-        <v>130</v>
-      </c>
-      <c r="G108" s="40">
+      <c r="H110" s="223"/>
+      <c r="I110" s="201"/>
+    </row>
+    <row r="111" spans="2:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B111" s="170"/>
+      <c r="C111" s="159"/>
+      <c r="D111" s="173"/>
+      <c r="E111" s="221"/>
+      <c r="F111" s="72" t="s">
+        <v>130</v>
+      </c>
+      <c r="G111" s="40">
         <v>46031</v>
       </c>
-      <c r="H108" s="94"/>
-      <c r="I108" s="135"/>
-    </row>
-    <row r="109" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B109" s="142" t="s">
+      <c r="H111" s="94"/>
+      <c r="I111" s="202"/>
+    </row>
+    <row r="112" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B112" s="209" t="s">
         <v>62</v>
       </c>
-      <c r="C109" s="143"/>
-      <c r="D109" s="143"/>
-      <c r="E109" s="143"/>
-      <c r="F109" s="143"/>
-      <c r="G109" s="143"/>
-      <c r="H109" s="143"/>
-      <c r="I109" s="126"/>
-    </row>
-    <row r="110" spans="2:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B110" s="32">
+      <c r="C112" s="210"/>
+      <c r="D112" s="210"/>
+      <c r="E112" s="210"/>
+      <c r="F112" s="210"/>
+      <c r="G112" s="210"/>
+      <c r="H112" s="210"/>
+      <c r="I112" s="126"/>
+    </row>
+    <row r="113" spans="2:9" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B113" s="32">
         <v>10.1</v>
       </c>
-      <c r="C110" s="52" t="s">
+      <c r="C113" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="D110" s="45"/>
-      <c r="E110" s="34" t="s">
-        <v>213</v>
-      </c>
-      <c r="F110" s="46" t="s">
-        <v>130</v>
-      </c>
-      <c r="G110" s="36">
+      <c r="D113" s="45"/>
+      <c r="E113" s="34" t="s">
+        <v>212</v>
+      </c>
+      <c r="F113" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="G113" s="36">
         <v>46009</v>
       </c>
-      <c r="H110" s="131"/>
-      <c r="I110" s="113" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="111" spans="2:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B111" s="32">
+      <c r="H113" s="131"/>
+      <c r="I113" s="113" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="114" spans="2:9" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B114" s="32">
         <v>10.199999999999999</v>
       </c>
-      <c r="C111" s="52" t="s">
+      <c r="C114" s="52" t="s">
         <v>42</v>
-      </c>
-      <c r="D111" s="45"/>
-      <c r="E111" s="34" t="s">
-        <v>214</v>
-      </c>
-      <c r="F111" s="46" t="s">
-        <v>130</v>
-      </c>
-      <c r="G111" s="36">
-        <v>46009</v>
-      </c>
-      <c r="H111" s="131"/>
-      <c r="I111" s="112" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="112" spans="2:9" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="18">
-        <v>10.3</v>
-      </c>
-      <c r="C112" s="54" t="s">
-        <v>43</v>
-      </c>
-      <c r="D112" s="124" t="s">
-        <v>215</v>
-      </c>
-      <c r="E112" s="124" t="s">
-        <v>216</v>
-      </c>
-      <c r="F112" s="130"/>
-      <c r="G112" s="132"/>
-      <c r="H112" s="106"/>
-      <c r="I112" s="129"/>
-    </row>
-    <row r="113" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B113" s="171" t="s">
-        <v>61</v>
-      </c>
-      <c r="C113" s="172"/>
-      <c r="D113" s="172"/>
-      <c r="E113" s="172"/>
-      <c r="F113" s="172"/>
-      <c r="G113" s="172"/>
-      <c r="H113" s="172"/>
-      <c r="I113" s="173"/>
-    </row>
-    <row r="114" spans="2:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B114" s="32">
-        <v>11.1</v>
-      </c>
-      <c r="C114" s="52" t="s">
-        <v>44</v>
       </c>
       <c r="D114" s="45"/>
       <c r="E114" s="34" t="s">
+        <v>213</v>
+      </c>
+      <c r="F114" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="G114" s="36">
+        <v>46009</v>
+      </c>
+      <c r="H114" s="131"/>
+      <c r="I114" s="112" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="115" spans="2:9" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B115" s="18">
+        <v>10.3</v>
+      </c>
+      <c r="C115" s="54" t="s">
+        <v>43</v>
+      </c>
+      <c r="D115" s="124" t="s">
+        <v>214</v>
+      </c>
+      <c r="E115" s="124" t="s">
+        <v>215</v>
+      </c>
+      <c r="F115" s="130"/>
+      <c r="G115" s="132"/>
+      <c r="H115" s="106"/>
+      <c r="I115" s="129"/>
+    </row>
+    <row r="116" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B116" s="138" t="s">
+        <v>61</v>
+      </c>
+      <c r="C116" s="139"/>
+      <c r="D116" s="139"/>
+      <c r="E116" s="139"/>
+      <c r="F116" s="139"/>
+      <c r="G116" s="139"/>
+      <c r="H116" s="139"/>
+      <c r="I116" s="140"/>
+    </row>
+    <row r="117" spans="2:9" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B117" s="32">
+        <v>11.1</v>
+      </c>
+      <c r="C117" s="52" t="s">
+        <v>44</v>
+      </c>
+      <c r="D117" s="45"/>
+      <c r="E117" s="34" t="s">
         <v>201</v>
       </c>
-      <c r="F114" s="46" t="s">
-        <v>130</v>
-      </c>
-      <c r="G114" s="36">
+      <c r="F117" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="G117" s="36">
         <v>46002</v>
       </c>
-      <c r="H114" s="92"/>
-      <c r="I114" s="112" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="115" spans="2:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B115" s="18">
+      <c r="H117" s="92"/>
+      <c r="I117" s="112" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="118" spans="2:9" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B118" s="18">
         <v>11.2</v>
       </c>
-      <c r="C115" s="54" t="s">
+      <c r="C118" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="D115" s="27"/>
-      <c r="E115" s="21" t="s">
+      <c r="D118" s="27"/>
+      <c r="E118" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="F115" s="56" t="s">
-        <v>130</v>
-      </c>
-      <c r="G115" s="57">
+      <c r="F118" s="56" t="s">
+        <v>130</v>
+      </c>
+      <c r="G118" s="57">
         <v>46002</v>
       </c>
-      <c r="H115" s="106"/>
-      <c r="I115" s="115" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="116" spans="2:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B116" s="32">
+      <c r="H118" s="106"/>
+      <c r="I118" s="115" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="119" spans="2:9" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B119" s="32">
         <v>11.3</v>
       </c>
-      <c r="C116" s="52" t="s">
+      <c r="C119" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="D116" s="45"/>
-      <c r="E116" s="35" t="s">
+      <c r="D119" s="45"/>
+      <c r="E119" s="35" t="s">
         <v>203</v>
       </c>
-      <c r="F116" s="46" t="s">
-        <v>130</v>
-      </c>
-      <c r="G116" s="36">
+      <c r="F119" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="G119" s="36">
         <v>46002</v>
       </c>
-      <c r="H116" s="92"/>
-      <c r="I116" s="112" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="117" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B117" s="171" t="s">
+      <c r="H119" s="92"/>
+      <c r="I119" s="112" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="120" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B120" s="138" t="s">
+        <v>224</v>
+      </c>
+      <c r="C120" s="139"/>
+      <c r="D120" s="139"/>
+      <c r="E120" s="139"/>
+      <c r="F120" s="139"/>
+      <c r="G120" s="139"/>
+      <c r="H120" s="139"/>
+      <c r="I120" s="140"/>
+    </row>
+    <row r="121" spans="2:9" ht="109.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B121" s="203">
+        <v>12.1</v>
+      </c>
+      <c r="C121" s="205" t="s">
         <v>208</v>
       </c>
-      <c r="C117" s="172"/>
-      <c r="D117" s="172"/>
-      <c r="E117" s="172"/>
-      <c r="F117" s="172"/>
-      <c r="G117" s="172"/>
-      <c r="H117" s="172"/>
-      <c r="I117" s="173"/>
-    </row>
-    <row r="118" spans="2:9" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B118" s="136">
-        <v>12.1</v>
-      </c>
-      <c r="C118" s="138" t="s">
-        <v>209</v>
-      </c>
-      <c r="D118" s="140"/>
-      <c r="E118" s="227" t="s">
+      <c r="D121" s="207"/>
+      <c r="E121" s="136" t="s">
+        <v>218</v>
+      </c>
+      <c r="F121" s="134" t="s">
+        <v>220</v>
+      </c>
+      <c r="G121" s="29">
+        <v>46028</v>
+      </c>
+      <c r="H121" s="135" t="s">
+        <v>221</v>
+      </c>
+      <c r="I121" s="200" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="122" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B122" s="203"/>
+      <c r="C122" s="205"/>
+      <c r="D122" s="207"/>
+      <c r="E122" s="137"/>
+      <c r="F122" s="42" t="s">
+        <v>130</v>
+      </c>
+      <c r="G122" s="29">
+        <v>46028</v>
+      </c>
+      <c r="H122" s="74"/>
+      <c r="I122" s="202"/>
+    </row>
+    <row r="123" spans="2:9" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B123" s="204"/>
+      <c r="C123" s="206"/>
+      <c r="D123" s="208"/>
+      <c r="E123" s="68" t="s">
         <v>219</v>
       </c>
-      <c r="F118" s="229" t="s">
-        <v>221</v>
-      </c>
-      <c r="G118" s="29">
+      <c r="F123" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="G123" s="62">
         <v>46028</v>
       </c>
-      <c r="H118" s="230" t="s">
+      <c r="H123" s="105"/>
+      <c r="I123" s="112" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="124" spans="2:9" ht="45.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B124" s="32">
+        <v>12.2</v>
+      </c>
+      <c r="C124" s="230" t="s">
         <v>222</v>
       </c>
-      <c r="I118" s="112" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="119" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B119" s="136"/>
-      <c r="C119" s="138"/>
-      <c r="D119" s="140"/>
-      <c r="E119" s="228"/>
-      <c r="F119" s="42" t="s">
-        <v>130</v>
-      </c>
-      <c r="G119" s="29">
-        <v>46028</v>
-      </c>
-      <c r="H119" s="74"/>
-      <c r="I119" s="112"/>
-    </row>
-    <row r="120" spans="2:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B120" s="137"/>
-      <c r="C120" s="139"/>
-      <c r="D120" s="141"/>
-      <c r="E120" s="68" t="s">
-        <v>220</v>
-      </c>
-      <c r="F120" s="53" t="s">
-        <v>130</v>
-      </c>
-      <c r="G120" s="62">
-        <v>46028</v>
-      </c>
-      <c r="H120" s="105"/>
-      <c r="I120" s="112" t="s">
-        <v>131</v>
-      </c>
+      <c r="D124" s="231"/>
+      <c r="E124" s="232" t="s">
+        <v>223</v>
+      </c>
+      <c r="F124" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="G124" s="36">
+        <v>46037</v>
+      </c>
+      <c r="H124" s="233"/>
+      <c r="I124" s="112" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="125" spans="2:9" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B125" s="235">
+        <v>12.3</v>
+      </c>
+      <c r="C125" s="236" t="s">
+        <v>226</v>
+      </c>
+      <c r="D125" s="237"/>
+      <c r="E125" s="133" t="s">
+        <v>227</v>
+      </c>
+      <c r="F125" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="G125" s="29">
+        <v>46038</v>
+      </c>
+      <c r="H125" s="135"/>
+      <c r="I125" s="200" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="126" spans="2:9" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B126" s="203"/>
+      <c r="C126" s="205"/>
+      <c r="D126" s="207"/>
+      <c r="E126" s="240" t="s">
+        <v>228</v>
+      </c>
+      <c r="F126" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="G126" s="29">
+        <v>46038</v>
+      </c>
+      <c r="H126" s="97"/>
+      <c r="I126" s="201"/>
+    </row>
+    <row r="127" spans="2:9" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B127" s="204"/>
+      <c r="C127" s="206"/>
+      <c r="D127" s="208"/>
+      <c r="E127" s="238" t="s">
+        <v>225</v>
+      </c>
+      <c r="F127" s="234" t="s">
+        <v>130</v>
+      </c>
+      <c r="G127" s="62">
+        <v>46038</v>
+      </c>
+      <c r="H127" s="239"/>
+      <c r="I127" s="202"/>
     </row>
   </sheetData>
-  <mergeCells count="129">
-    <mergeCell ref="E118:E119"/>
-    <mergeCell ref="B117:I117"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="I38:I39"/>
-    <mergeCell ref="E76:E77"/>
-    <mergeCell ref="H65:H67"/>
-    <mergeCell ref="E70:E71"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="I65:I68"/>
-    <mergeCell ref="E79:E82"/>
-    <mergeCell ref="I79:I82"/>
-    <mergeCell ref="I19:I21"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="I34:I36"/>
-    <mergeCell ref="I70:I71"/>
-    <mergeCell ref="I72:I73"/>
-    <mergeCell ref="I74:I75"/>
-    <mergeCell ref="I86:I88"/>
-    <mergeCell ref="D69:D73"/>
+  <mergeCells count="138">
+    <mergeCell ref="I121:I122"/>
+    <mergeCell ref="B125:B127"/>
+    <mergeCell ref="C125:C127"/>
+    <mergeCell ref="D125:D127"/>
+    <mergeCell ref="I125:I127"/>
+    <mergeCell ref="I109:I111"/>
+    <mergeCell ref="B121:B123"/>
+    <mergeCell ref="C121:C123"/>
+    <mergeCell ref="D121:D123"/>
+    <mergeCell ref="B112:H112"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B56:H56"/>
+    <mergeCell ref="B109:B111"/>
+    <mergeCell ref="C109:C111"/>
+    <mergeCell ref="D109:D111"/>
+    <mergeCell ref="E109:E111"/>
+    <mergeCell ref="H109:H110"/>
+    <mergeCell ref="B67:H67"/>
+    <mergeCell ref="B88:H88"/>
+    <mergeCell ref="B77:B81"/>
+    <mergeCell ref="B82:B87"/>
+    <mergeCell ref="B101:G101"/>
+    <mergeCell ref="B107:B108"/>
+    <mergeCell ref="E107:E108"/>
+    <mergeCell ref="E98:E99"/>
+    <mergeCell ref="D92:D93"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="B100:H100"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="I64:I65"/>
+    <mergeCell ref="I98:I99"/>
+    <mergeCell ref="B116:I116"/>
+    <mergeCell ref="I86:I87"/>
+    <mergeCell ref="B68:B71"/>
+    <mergeCell ref="C68:C71"/>
+    <mergeCell ref="D68:D71"/>
+    <mergeCell ref="E68:E71"/>
+    <mergeCell ref="E77:E78"/>
+    <mergeCell ref="B72:B76"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="D37:D39"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="D63:D65"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="B63:B65"/>
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="E86:E87"/>
+    <mergeCell ref="D96:D99"/>
+    <mergeCell ref="C96:C99"/>
+    <mergeCell ref="I79:I80"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="B89:B91"/>
+    <mergeCell ref="C77:C81"/>
+    <mergeCell ref="D77:D81"/>
+    <mergeCell ref="D82:D87"/>
+    <mergeCell ref="C82:C87"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C33:C36"/>
+    <mergeCell ref="D33:D36"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="D89:D91"/>
+    <mergeCell ref="C72:C76"/>
+    <mergeCell ref="C89:C91"/>
+    <mergeCell ref="E75:E76"/>
+    <mergeCell ref="B61:H61"/>
+    <mergeCell ref="B49:B51"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="D49:D51"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="B96:B99"/>
+    <mergeCell ref="I107:I108"/>
+    <mergeCell ref="B102:B105"/>
+    <mergeCell ref="C102:C105"/>
+    <mergeCell ref="D102:D105"/>
+    <mergeCell ref="E104:E105"/>
+    <mergeCell ref="E102:E103"/>
+    <mergeCell ref="I102:I103"/>
+    <mergeCell ref="I104:I105"/>
+    <mergeCell ref="D107:D108"/>
+    <mergeCell ref="C107:C108"/>
+    <mergeCell ref="I49:I51"/>
+    <mergeCell ref="I77:I78"/>
+    <mergeCell ref="I89:I91"/>
+    <mergeCell ref="D72:D76"/>
     <mergeCell ref="D40:D41"/>
     <mergeCell ref="K6:L6"/>
     <mergeCell ref="B9:B12"/>
@@ -4863,87 +5142,30 @@
     <mergeCell ref="C15:C16"/>
     <mergeCell ref="D15:D16"/>
     <mergeCell ref="C19:C21"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="B89:B90"/>
-    <mergeCell ref="B93:B96"/>
-    <mergeCell ref="I104:I105"/>
-    <mergeCell ref="B99:B102"/>
-    <mergeCell ref="C99:C102"/>
-    <mergeCell ref="D99:D102"/>
-    <mergeCell ref="E101:E102"/>
-    <mergeCell ref="E99:E100"/>
-    <mergeCell ref="I99:I100"/>
-    <mergeCell ref="I101:I102"/>
-    <mergeCell ref="D104:D105"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="D27:D29"/>
-    <mergeCell ref="B31:H31"/>
-    <mergeCell ref="B86:B88"/>
-    <mergeCell ref="C74:C78"/>
-    <mergeCell ref="D74:D78"/>
-    <mergeCell ref="D79:D84"/>
-    <mergeCell ref="C79:C84"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C33:C36"/>
-    <mergeCell ref="D33:D36"/>
-    <mergeCell ref="B33:B36"/>
-    <mergeCell ref="E34:E36"/>
-    <mergeCell ref="D86:D88"/>
-    <mergeCell ref="C69:C73"/>
-    <mergeCell ref="C86:C88"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="B58:H58"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="I95:I96"/>
-    <mergeCell ref="B113:I113"/>
-    <mergeCell ref="I83:I84"/>
-    <mergeCell ref="B65:B68"/>
-    <mergeCell ref="C65:C68"/>
-    <mergeCell ref="D65:D68"/>
-    <mergeCell ref="E65:E68"/>
-    <mergeCell ref="E74:E75"/>
-    <mergeCell ref="B69:B73"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="D37:D39"/>
-    <mergeCell ref="C37:C39"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="D60:D62"/>
-    <mergeCell ref="C60:C62"/>
-    <mergeCell ref="B60:B62"/>
-    <mergeCell ref="E61:E62"/>
-    <mergeCell ref="E83:E84"/>
-    <mergeCell ref="D93:D96"/>
-    <mergeCell ref="C93:C96"/>
-    <mergeCell ref="I76:I77"/>
-    <mergeCell ref="I106:I108"/>
-    <mergeCell ref="B118:B120"/>
-    <mergeCell ref="C118:C120"/>
-    <mergeCell ref="D118:D120"/>
-    <mergeCell ref="B109:H109"/>
-    <mergeCell ref="B44:H44"/>
-    <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B53:H53"/>
-    <mergeCell ref="B106:B108"/>
-    <mergeCell ref="C106:C108"/>
-    <mergeCell ref="D106:D108"/>
-    <mergeCell ref="E106:E108"/>
-    <mergeCell ref="H106:H107"/>
-    <mergeCell ref="B64:H64"/>
-    <mergeCell ref="B85:H85"/>
-    <mergeCell ref="B74:B78"/>
-    <mergeCell ref="B79:B84"/>
-    <mergeCell ref="B98:G98"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="E104:E105"/>
-    <mergeCell ref="E95:E96"/>
-    <mergeCell ref="D89:D90"/>
-    <mergeCell ref="C89:C90"/>
-    <mergeCell ref="B97:H97"/>
+    <mergeCell ref="E121:E122"/>
+    <mergeCell ref="B120:I120"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="I38:I39"/>
+    <mergeCell ref="E79:E80"/>
+    <mergeCell ref="H68:H70"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="I68:I71"/>
+    <mergeCell ref="E82:E85"/>
+    <mergeCell ref="I82:I85"/>
+    <mergeCell ref="I19:I21"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="I34:I36"/>
+    <mergeCell ref="I73:I74"/>
+    <mergeCell ref="I75:I76"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
